--- a/JsonConverter/ExcelFiles/0_MindDialogue.xlsx
+++ b/JsonConverter/ExcelFiles/0_MindDialogue.xlsx
@@ -8,24 +8,21 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\0_SonghaUnityGame\JsonConverter\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC7C18EA-52AD-4AC9-8941-520D705E8F42}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1C04F64-999C-4F55-9224-216D08891F93}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="12510" yWindow="1425" windowWidth="14385" windowHeight="14055" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1950" yWindow="1740" windowWidth="23505" windowHeight="14460" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="DNTable_Weapon" sheetId="1" r:id="rId1"/>
+    <sheet name="Table_MindDialogue" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="40">
   <si>
     <t>서로의 일상이 바쁘긴했지만 나는 정말로 지금이 서로가 서로에게 떳떳하게 살아가는 일상이고, 어른이 되어가는 과정이라고 생각했다. &lt;np&gt;하지만 그녀는 다르게 생각했나보다.</t>
-  </si>
-  <si>
-    <t>오늘도 그녀와 함께 새벽까지 게임을 하고, 잘 준비를 하며 하루를 마무리하는 카톡을 하였다.</t>
   </si>
   <si>
     <t xml:space="preserve">그렇게 2년이 지났고, 나는 여전히 우리는 끈끈하고 서로를 아껴주고, 사랑을 주며 살아갔다고, 비록 바쁜 일상이 되었지만 서로에게 만큼은 진심이라고 생각했다.&lt;np&gt;
@@ -71,32 +68,8 @@
     <t>잠깐 전화 하자는 그녀의 카톡이 도착했다.&lt;np&gt;전부터 전화를 하며 잠드는 루틴을 가진 우리였다.&lt;np&gt;그렇지만 최근 서로 바쁘고, 다른 일정을 가지고 있어 근래에는 전화를 하지 않았었다.&lt;np&gt;전화를 받자 무언가 감정을 다 잡은 듯한 목소리톤과 평소와는 다른 분위기가 느껴졌다.</t>
   </si>
   <si>
-    <t>mindDialogue_Opening_1_1_100</t>
-  </si>
-  <si>
-    <t>mindDialogue_Opening_1_1_101</t>
-  </si>
-  <si>
-    <t>mindDialogue_Opening_1_1_105</t>
-  </si>
-  <si>
-    <t>mindDialogue_Opening_1_1_102</t>
-  </si>
-  <si>
-    <t>mindDialogue_Opening_1_1_106</t>
-  </si>
-  <si>
-    <t>mindDialogue_Opening_1_1_107</t>
-  </si>
-  <si>
     <t xml:space="preserve">말을 듣다보니 나도 모르게 눈물이 흘렀다.&lt;np&gt; 우리의 1600일이라는 숫자는 그저 극복 할 가치가 없는 이별 해야만 하는 이유가 되는것이 너무 슬프고, 마음이 아팠다.&lt;np&gt;목이 매여서 한동안 말을 하지 못했다....
 </t>
-  </si>
-  <si>
-    <t>mindDialogue_Opening_1_1_103</t>
-  </si>
-  <si>
-    <t>mindDialogue_Opening_1_1_104</t>
   </si>
   <si>
     <t xml:space="preserve">나는 처음으로 그녀에게 사랑이 식었다는 얘기를 들었다. 아무리 힘든 상황이었어도, 아무리 심하게 싸운 날도, 그녀는 나를 좋아한다고 해주었다.&lt;np&gt;처음으로 들은 그 이야기는 나에게는 너무 충격으로 돌아왔지만, 나는 그녀를 잃고 싶지 않았다. 
@@ -139,6 +112,70 @@
   </si>
   <si>
     <t>NextDialogueId</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>mindDialogue_Opening_1_1_103</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>mindDialogue_Opening_1_1_107</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>mindDialogue_Opening_1_1_112</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>mindDialogue_Opening_1_1_115</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>mindDialogue_Opening_1_1_119</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>mindDialogue_Opening_1_1_122</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>mindDialogue_Opening_1_1_128</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>normalDialogue_opening_1_1_104</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>normalDialogue_opening_1_1_110</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>normalDialogue_opening_1_1_113</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>normalDialogue_opening_1_1_116</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>normalDialogue_opening_1_1_120</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>msgDialogue_Opening_1_1_123</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>mindDialogue_Opening_1_1_99</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>msgDialogue_Opening_1_1_100</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>오늘도 그녀와 함께 새벽까지 게임을 하고, 잘 준비를 하며 하루를 마무리하는 카톡을 하였다.</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -690,8 +727,8 @@
   <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="36.5703125" style="5" customWidth="1"/>
-    <col min="2" max="2" width="55.42578125" style="5" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="29.7109375" style="5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="80" style="5" customWidth="1"/>
+    <col min="3" max="3" width="34.28515625" style="5" customWidth="1"/>
     <col min="4" max="5" width="77.140625" style="5" customWidth="1"/>
     <col min="6" max="7" width="50.7109375" style="5" customWidth="1"/>
     <col min="8" max="16384" width="12.5703125" style="5"/>
@@ -699,7 +736,7 @@
   <sheetData>
     <row r="1" spans="1:8" ht="15.75" customHeight="1">
       <c r="A1" s="4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B1" s="4"/>
       <c r="C1" s="4"/>
@@ -710,78 +747,82 @@
     </row>
     <row r="2" spans="1:8" ht="15.75" customHeight="1">
       <c r="A2" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B2" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="B2" s="4" t="s">
-        <v>13</v>
-      </c>
       <c r="C2" s="4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="15.75" customHeight="1">
       <c r="A3" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="D3" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="E3" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="C3" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="D3" s="6" t="s">
+      <c r="F3" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="G3" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="H3" s="6" t="s">
         <v>3</v>
-      </c>
-      <c r="E3" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="F3" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="G3" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="H3" s="6" t="s">
-        <v>4</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="15.75" customHeight="1">
       <c r="A4" s="1" t="s">
-        <v>15</v>
+        <v>37</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C4" s="1"/>
+        <v>39</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>38</v>
+      </c>
       <c r="F4" s="1" t="s">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="G4" s="1"/>
       <c r="H4" s="7"/>
     </row>
     <row r="5" spans="1:8" ht="15.75" customHeight="1">
       <c r="A5" s="1" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="C5" s="1"/>
+        <v>13</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>31</v>
+      </c>
       <c r="D5" s="1"/>
       <c r="E5" s="1"/>
       <c r="F5" s="1"/>
@@ -790,13 +831,13 @@
     </row>
     <row r="6" spans="1:8" ht="15.75" customHeight="1">
       <c r="A6" s="1" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>0</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="D6" s="1"/>
       <c r="E6" s="1"/>
@@ -806,12 +847,14 @@
     </row>
     <row r="7" spans="1:8" ht="15.75" customHeight="1">
       <c r="A7" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="C7" s="1"/>
+        <v>21</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>19</v>
+      </c>
       <c r="D7" s="1"/>
       <c r="E7" s="1"/>
       <c r="F7" s="1"/>
@@ -820,12 +863,14 @@
     </row>
     <row r="8" spans="1:8" ht="15.75" customHeight="1">
       <c r="A8" s="1" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="C8" s="2"/>
+        <v>1</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>32</v>
+      </c>
       <c r="D8" s="2"/>
       <c r="E8" s="2"/>
       <c r="F8" s="2"/>
@@ -834,12 +879,14 @@
     </row>
     <row r="9" spans="1:8" ht="15.75" customHeight="1">
       <c r="A9" s="1" t="s">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="C9" s="2"/>
+        <v>15</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>33</v>
+      </c>
       <c r="D9" s="2"/>
       <c r="E9" s="2"/>
       <c r="F9" s="2"/>
@@ -848,12 +895,14 @@
     </row>
     <row r="10" spans="1:8" ht="15.75" customHeight="1">
       <c r="A10" s="1" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="C10" s="3"/>
+        <v>14</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>34</v>
+      </c>
       <c r="D10" s="3"/>
       <c r="E10" s="3"/>
       <c r="F10" s="3"/>
@@ -862,12 +911,14 @@
     </row>
     <row r="11" spans="1:8" ht="15.75" customHeight="1">
       <c r="A11" s="3" t="s">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="C11" s="3"/>
+        <v>16</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>35</v>
+      </c>
       <c r="D11" s="3"/>
       <c r="E11" s="3"/>
       <c r="F11" s="3"/>
@@ -876,12 +927,14 @@
     </row>
     <row r="12" spans="1:8" ht="15.75" customHeight="1">
       <c r="A12" s="2" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="C12" s="2"/>
+        <v>17</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>36</v>
+      </c>
       <c r="D12" s="2"/>
       <c r="E12" s="2"/>
       <c r="F12" s="2"/>
@@ -890,10 +943,10 @@
     </row>
     <row r="13" spans="1:8" ht="15.75" customHeight="1">
       <c r="A13" s="1" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="C13" s="1"/>
       <c r="D13" s="1"/>

--- a/JsonConverter/ExcelFiles/0_MindDialogue.xlsx
+++ b/JsonConverter/ExcelFiles/0_MindDialogue.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\0_SonghaUnityGame\JsonConverter\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1C04F64-999C-4F55-9224-216D08891F93}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56219B71-27CA-41A7-8E59-E2A23D746802}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1950" yWindow="1740" windowWidth="23505" windowHeight="14460" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3510" yWindow="2550" windowWidth="23505" windowHeight="13650" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Table_MindDialogue" sheetId="1" r:id="rId1"/>
@@ -85,14 +85,6 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>mindDialogue_Opening_1_1_108</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>mindDialogue_Opening_1_1_109</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>그렇게 나의 세상은 무너졌다. &lt;np&gt;예상치 못한 타이밍과 잡을 수 없는 이 무력함에 밤새 울며 새벽을 보냈다. 너무 어버버 이별한 것 같다는 생각이 들었다.</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -115,67 +107,60 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
+    <t>오늘도 그녀와 함께 새벽까지 게임을 하고, 잘 준비를 하며 하루를 마무리하는 카톡을 하였다.</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>normalDialogue_Opening_1_1_104</t>
+  </si>
+  <si>
     <t>mindDialogue_Opening_1_1_103</t>
-    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>mindDialogue_Opening_1_1_107</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>mindDialogue_Opening_1_1_108</t>
+  </si>
+  <si>
+    <t>mindDialogue_Opening_1_1_109</t>
+  </si>
+  <si>
+    <t>normalDialogue_Opening_1_1_110</t>
   </si>
   <si>
     <t>mindDialogue_Opening_1_1_112</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>normalDialogue_Opening_1_1_113</t>
   </si>
   <si>
     <t>mindDialogue_Opening_1_1_115</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>normalDialogue_Opening_1_1_116</t>
   </si>
   <si>
     <t>mindDialogue_Opening_1_1_119</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>normalDialogue_Opening_1_1_120</t>
   </si>
   <si>
     <t>mindDialogue_Opening_1_1_122</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>msgDialogue_Opening_1_1_123</t>
   </si>
   <si>
     <t>mindDialogue_Opening_1_1_128</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>normalDialogue_opening_1_1_104</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>normalDialogue_opening_1_1_110</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>normalDialogue_opening_1_1_113</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>normalDialogue_opening_1_1_116</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>normalDialogue_opening_1_1_120</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>msgDialogue_Opening_1_1_123</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>mindDialogue_Opening_1_1_99</t>
-    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>msgDialogue_Opening_1_1_100</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>오늘도 그녀와 함께 새벽까지 게임을 하고, 잘 준비를 하며 하루를 마무리하는 카톡을 하였다.</t>
+    <t>mindDialogue_Opening_1_1_99</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -779,7 +764,7 @@
         <v>6</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D3" s="6" t="s">
         <v>2</v>
@@ -799,16 +784,16 @@
     </row>
     <row r="4" spans="1:8" ht="15.75" customHeight="1">
       <c r="A4" s="1" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>39</v>
+        <v>22</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>38</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="G4" s="1"/>
       <c r="H4" s="7"/>
@@ -821,7 +806,7 @@
         <v>13</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="D5" s="1"/>
       <c r="E5" s="1"/>
@@ -837,7 +822,7 @@
         <v>0</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="D6" s="1"/>
       <c r="E6" s="1"/>
@@ -847,13 +832,13 @@
     </row>
     <row r="7" spans="1:8" ht="15.75" customHeight="1">
       <c r="A7" s="1" t="s">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="D7" s="1"/>
       <c r="E7" s="1"/>
@@ -863,13 +848,13 @@
     </row>
     <row r="8" spans="1:8" ht="15.75" customHeight="1">
       <c r="A8" s="1" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>1</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="D8" s="2"/>
       <c r="E8" s="2"/>
@@ -879,13 +864,13 @@
     </row>
     <row r="9" spans="1:8" ht="15.75" customHeight="1">
       <c r="A9" s="1" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="D9" s="2"/>
       <c r="E9" s="2"/>
@@ -895,13 +880,13 @@
     </row>
     <row r="10" spans="1:8" ht="15.75" customHeight="1">
       <c r="A10" s="1" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="B10" s="3" t="s">
         <v>14</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D10" s="3"/>
       <c r="E10" s="3"/>
@@ -911,13 +896,13 @@
     </row>
     <row r="11" spans="1:8" ht="15.75" customHeight="1">
       <c r="A11" s="3" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="B11" s="3" t="s">
         <v>16</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D11" s="3"/>
       <c r="E11" s="3"/>
@@ -927,7 +912,7 @@
     </row>
     <row r="12" spans="1:8" ht="15.75" customHeight="1">
       <c r="A12" s="2" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>17</v>
@@ -943,10 +928,10 @@
     </row>
     <row r="13" spans="1:8" ht="15.75" customHeight="1">
       <c r="A13" s="1" t="s">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C13" s="1"/>
       <c r="D13" s="1"/>

--- a/JsonConverter/ExcelFiles/0_MindDialogue.xlsx
+++ b/JsonConverter/ExcelFiles/0_MindDialogue.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\0_SonghaUnityGame\JsonConverter\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9B29FCE-F779-453F-A5D4-4600A4816046}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8603E63A-D824-498C-885E-F97478049B29}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1545" yWindow="2550" windowWidth="27255" windowHeight="13650" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="27255" windowHeight="13650" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Table_MindDialogue" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="86">
   <si>
     <t>CharacterDataId</t>
   </si>
@@ -65,10 +65,6 @@
     <t>string</t>
   </si>
   <si>
-    <t>그렇게 나의 세상은 무너졌다. &lt;np&gt;예상치 못한 타이밍과 잡을 수 없는 이 무력함에 밤새 울며 새벽을 보냈다. 너무 어버버 이별한 것 같다는 생각이 들었다.</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>Texture2D/Texture2D_Loading_1</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -162,16 +158,6 @@
   </si>
   <si>
     <t xml:space="preserve">그래서 그녀도 다시 생각을 하게 되었고, 이대로 가다간 서로 발전도 없이 20대 후반을 맞이 할거 같다고 하였다. </t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>그렇게 그녀는 훈련소에 있는 수화기 너머로 나에게 이야기를 전하였다.
-정말 무력하게 이야기를 들었지만 현실과 타협하듯 그녀에게 "그럼 딱 우리 이번 년도까지만 만나자. 내가 변화된 모습을 보여주고, 너의 맘도 변화 시킬 수 있지않을까? 딱 이번년도까지만 만나자.."
-라고 대답하였다.</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>말 없이 울고 있는 그녀와 수화기 너머로 듣고 있는 나는 마치 영화 주인공이 된 듯. 세상에서 가장 슬픈 모습으로 서로에게 눈물을 전하였다.</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
@@ -312,18 +298,10 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>그렇게 강력하게 매번 붙잡았던 나는 더이상 좋지 않다는 말에 무너기에 충분했다.&lt;np&gt;&lt;np&gt;&lt;np&gt;</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>아니.. 잡을 수 없었다..</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>mindDialogue_Opening_1_1_154</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>mindDialogue_Opening_1_1_160</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -352,6 +330,42 @@
   </si>
   <si>
     <t>mindDialogue_Opening_1_1_171</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>그렇게 강력하게 매번 붙잡았던 나는 더이상 좋지 않다는 말에 무너지기에 충분했다.</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>말 없이 울고 있는 그녀와 수화기 너머로 듣고 있는 나는 마치 영화 주인공이 된 듯 세상에서 가장 슬픈 모습으로 서로에게 눈물을 전하였다.</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>mindDialogue_Opening_1_1_122(2)</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>"그럼 딱 우리 이번 년도까지만 만나자. 내가 변화된 모습을 보여주고, 너의 맘도 변화 시킬 수 있지않을까? 딱 이번년도까지만 만나자.." 라고 대답하였다.</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">그렇게 그녀는 훈련소에 있는 수화기 너머로 나에게 이야기를 전하였다. 정말 무력하게 이야기를 들었지만 현실과 타협하듯 그녀에게 </t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>normalDialogue_Opening_1_1_154</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>그렇게 나의 세상은 무너졌다. .</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>mindDialogue_Opening_1_1_172</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>예상치 못한 타이밍과 잡을 수 없는 이 무력함에 밤새 울며 새벽을 보냈다. 너무 어버버 이별한 것 같다는 생각이 들었다.</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -899,7 +913,7 @@
   <sheetPr codeName="Sheet1">
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:H1020"/>
+  <dimension ref="A1:H1021"/>
   <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="36.5703125" style="5" customWidth="1"/>
@@ -932,7 +946,7 @@
         <v>9</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E2" s="4" t="s">
         <v>4</v>
@@ -955,7 +969,7 @@
         <v>3</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D3" s="6"/>
       <c r="E3" s="6" t="s">
@@ -973,29 +987,29 @@
     </row>
     <row r="4" spans="1:8" ht="15.75" customHeight="1">
       <c r="A4" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C4" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="B4" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>16</v>
-      </c>
       <c r="F4" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G4" s="1"/>
       <c r="H4" s="7"/>
     </row>
     <row r="5" spans="1:8" ht="15.75" customHeight="1">
       <c r="A5" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B5" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C5" s="1" t="s">
         <v>21</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>22</v>
       </c>
       <c r="D5" s="1"/>
       <c r="E5" s="1"/>
@@ -1005,13 +1019,13 @@
     </row>
     <row r="6" spans="1:8" ht="15.75" customHeight="1">
       <c r="A6" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C6" s="1" t="s">
         <v>22</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>23</v>
       </c>
       <c r="D6" s="1"/>
       <c r="E6" s="1"/>
@@ -1021,13 +1035,13 @@
     </row>
     <row r="7" spans="1:8" ht="15.75" customHeight="1">
       <c r="A7" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C7" s="1" t="s">
         <v>23</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>24</v>
       </c>
       <c r="D7" s="1"/>
       <c r="E7" s="1"/>
@@ -1037,13 +1051,13 @@
     </row>
     <row r="8" spans="1:8" ht="15.75" customHeight="1">
       <c r="A8" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C8" s="1" t="s">
         <v>24</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>25</v>
       </c>
       <c r="D8" s="1"/>
       <c r="E8" s="1"/>
@@ -1053,13 +1067,13 @@
     </row>
     <row r="9" spans="1:8" ht="15.75" customHeight="1">
       <c r="A9" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C9" s="1" t="s">
         <v>26</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>27</v>
       </c>
       <c r="D9" s="1"/>
       <c r="E9" s="1"/>
@@ -1069,13 +1083,13 @@
     </row>
     <row r="10" spans="1:8" ht="15.75" customHeight="1">
       <c r="A10" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B10" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C10" s="1" t="s">
         <v>29</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>30</v>
       </c>
       <c r="D10" s="1"/>
       <c r="E10" s="1"/>
@@ -1085,13 +1099,13 @@
     </row>
     <row r="11" spans="1:8" ht="15.75" customHeight="1">
       <c r="A11" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="D11" s="1"/>
       <c r="E11" s="1"/>
@@ -1101,13 +1115,13 @@
     </row>
     <row r="12" spans="1:8" ht="15.75" customHeight="1">
       <c r="A12" s="1" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="D12" s="1"/>
       <c r="E12" s="1"/>
@@ -1117,13 +1131,13 @@
     </row>
     <row r="13" spans="1:8" ht="15.75" customHeight="1">
       <c r="A13" s="1" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="D13" s="1"/>
       <c r="E13" s="1"/>
@@ -1133,13 +1147,13 @@
     </row>
     <row r="14" spans="1:8" ht="15.75" customHeight="1">
       <c r="A14" s="1" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="D14" s="1"/>
       <c r="E14" s="1"/>
@@ -1149,13 +1163,13 @@
     </row>
     <row r="15" spans="1:8" ht="15.75" customHeight="1">
       <c r="A15" s="1" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>35</v>
+        <v>81</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>43</v>
+        <v>79</v>
       </c>
       <c r="D15" s="1"/>
       <c r="E15" s="1"/>
@@ -1165,13 +1179,13 @@
     </row>
     <row r="16" spans="1:8" ht="15.75" customHeight="1">
       <c r="A16" s="1" t="s">
-        <v>43</v>
+        <v>79</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>36</v>
+        <v>80</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="D16" s="1"/>
       <c r="E16" s="1"/>
@@ -1181,13 +1195,13 @@
     </row>
     <row r="17" spans="1:8" ht="15.75" customHeight="1">
       <c r="A17" s="1" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>37</v>
+        <v>78</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="D17" s="1"/>
       <c r="E17" s="1"/>
@@ -1197,29 +1211,29 @@
     </row>
     <row r="18" spans="1:8" ht="15.75" customHeight="1">
       <c r="A18" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="D18" s="2"/>
-      <c r="E18" s="2"/>
-      <c r="F18" s="2"/>
-      <c r="G18" s="2"/>
-      <c r="H18" s="2"/>
+        <v>41</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="D18" s="1"/>
+      <c r="E18" s="1"/>
+      <c r="F18" s="1"/>
+      <c r="G18" s="1"/>
+      <c r="H18" s="1"/>
     </row>
     <row r="19" spans="1:8" ht="15.75" customHeight="1">
       <c r="A19" s="1" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="D19" s="2"/>
       <c r="E19" s="2"/>
@@ -1229,13 +1243,13 @@
     </row>
     <row r="20" spans="1:8" ht="15.75" customHeight="1">
       <c r="A20" s="1" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>46</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="D20" s="2"/>
       <c r="E20" s="2"/>
@@ -1245,13 +1259,13 @@
     </row>
     <row r="21" spans="1:8" ht="15.75" customHeight="1">
       <c r="A21" s="1" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="D21" s="2"/>
       <c r="E21" s="2"/>
@@ -1261,29 +1275,29 @@
     </row>
     <row r="22" spans="1:8" ht="15.75" customHeight="1">
       <c r="A22" s="1" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>56</v>
+        <v>44</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="D22" s="2"/>
       <c r="E22" s="2"/>
       <c r="F22" s="2"/>
-      <c r="G22" s="1"/>
-      <c r="H22" s="1"/>
+      <c r="G22" s="2"/>
+      <c r="H22" s="2"/>
     </row>
     <row r="23" spans="1:8" ht="15.75" customHeight="1">
       <c r="A23" s="1" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D23" s="2"/>
       <c r="E23" s="2"/>
@@ -1293,29 +1307,29 @@
     </row>
     <row r="24" spans="1:8" ht="15.75" customHeight="1">
       <c r="A24" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="B24" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="C24" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="D24" s="3"/>
-      <c r="E24" s="3"/>
-      <c r="F24" s="3"/>
-      <c r="G24" s="3"/>
-      <c r="H24" s="3"/>
+        <v>54</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="D24" s="2"/>
+      <c r="E24" s="2"/>
+      <c r="F24" s="2"/>
+      <c r="G24" s="1"/>
+      <c r="H24" s="1"/>
     </row>
     <row r="25" spans="1:8" ht="15.75" customHeight="1">
       <c r="A25" s="1" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="D25" s="3"/>
       <c r="E25" s="3"/>
@@ -1325,13 +1339,13 @@
     </row>
     <row r="26" spans="1:8" ht="15.75" customHeight="1">
       <c r="A26" s="1" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>79</v>
+        <v>58</v>
       </c>
       <c r="D26" s="3"/>
       <c r="E26" s="3"/>
@@ -1340,14 +1354,14 @@
       <c r="H26" s="3"/>
     </row>
     <row r="27" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A27" s="3" t="s">
-        <v>65</v>
+      <c r="A27" s="1" t="s">
+        <v>58</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>71</v>
+        <v>60</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>66</v>
+        <v>74</v>
       </c>
       <c r="D27" s="3"/>
       <c r="E27" s="3"/>
@@ -1357,13 +1371,13 @@
     </row>
     <row r="28" spans="1:8" ht="15.75" customHeight="1">
       <c r="A28" s="3" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="D28" s="3"/>
       <c r="E28" s="3"/>
@@ -1373,13 +1387,13 @@
     </row>
     <row r="29" spans="1:8" ht="15.75" customHeight="1">
       <c r="A29" s="3" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="D29" s="3"/>
       <c r="E29" s="3"/>
@@ -1389,13 +1403,13 @@
     </row>
     <row r="30" spans="1:8" ht="15.75" customHeight="1">
       <c r="A30" s="3" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="D30" s="3"/>
       <c r="E30" s="3"/>
@@ -1404,30 +1418,30 @@
       <c r="H30" s="3"/>
     </row>
     <row r="31" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A31" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="B31" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="C31" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="D31" s="2"/>
-      <c r="E31" s="2"/>
-      <c r="F31" s="2"/>
-      <c r="G31" s="2"/>
-      <c r="H31" s="2"/>
+      <c r="A31" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="C31" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="D31" s="3"/>
+      <c r="E31" s="3"/>
+      <c r="F31" s="3"/>
+      <c r="G31" s="3"/>
+      <c r="H31" s="3"/>
     </row>
     <row r="32" spans="1:8" ht="15.75" customHeight="1">
       <c r="A32" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="C32" s="2" t="s">
         <v>75</v>
-      </c>
-      <c r="B32" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="C32" s="2" t="s">
-        <v>78</v>
       </c>
       <c r="D32" s="2"/>
       <c r="E32" s="2"/>
@@ -1436,32 +1450,44 @@
       <c r="H32" s="2"/>
     </row>
     <row r="33" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A33" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="B33" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C33" s="1"/>
-      <c r="D33" s="1"/>
-      <c r="E33" s="1"/>
-      <c r="F33" s="1"/>
-      <c r="G33" s="1"/>
-      <c r="H33" s="1"/>
+      <c r="A33" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="B33" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="D33" s="2"/>
+      <c r="E33" s="2"/>
+      <c r="F33" s="2"/>
+      <c r="G33" s="2"/>
+      <c r="H33" s="2"/>
     </row>
     <row r="34" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A34" s="3"/>
-      <c r="B34" s="3"/>
-      <c r="C34" s="3"/>
-      <c r="D34" s="3"/>
-      <c r="E34" s="3"/>
-      <c r="F34" s="3"/>
-      <c r="G34" s="3"/>
-      <c r="H34" s="3"/>
+      <c r="A34" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="D34" s="1"/>
+      <c r="E34" s="1"/>
+      <c r="F34" s="1"/>
+      <c r="G34" s="1"/>
+      <c r="H34" s="1"/>
     </row>
     <row r="35" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A35" s="3"/>
-      <c r="B35" s="3"/>
+      <c r="A35" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="B35" s="3" t="s">
+        <v>85</v>
+      </c>
       <c r="C35" s="3"/>
       <c r="D35" s="3"/>
       <c r="E35" s="3"/>
@@ -1470,14 +1496,14 @@
       <c r="H35" s="3"/>
     </row>
     <row r="36" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A36" s="8"/>
-      <c r="B36" s="8"/>
-      <c r="C36" s="8"/>
-      <c r="D36" s="8"/>
-      <c r="E36" s="8"/>
-      <c r="F36" s="8"/>
-      <c r="G36" s="8"/>
-      <c r="H36" s="8"/>
+      <c r="A36" s="3"/>
+      <c r="B36" s="3"/>
+      <c r="C36" s="3"/>
+      <c r="D36" s="3"/>
+      <c r="E36" s="3"/>
+      <c r="F36" s="3"/>
+      <c r="G36" s="3"/>
+      <c r="H36" s="3"/>
     </row>
     <row r="37" spans="1:8" ht="15.75" customHeight="1">
       <c r="A37" s="8"/>
@@ -1570,14 +1596,14 @@
       <c r="H45" s="8"/>
     </row>
     <row r="46" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A46" s="9"/>
-      <c r="B46" s="9"/>
-      <c r="C46" s="9"/>
-      <c r="D46" s="9"/>
-      <c r="E46" s="9"/>
-      <c r="F46" s="9"/>
-      <c r="G46" s="9"/>
-      <c r="H46" s="9"/>
+      <c r="A46" s="8"/>
+      <c r="B46" s="8"/>
+      <c r="C46" s="8"/>
+      <c r="D46" s="8"/>
+      <c r="E46" s="8"/>
+      <c r="F46" s="8"/>
+      <c r="G46" s="8"/>
+      <c r="H46" s="8"/>
     </row>
     <row r="47" spans="1:8" ht="15.75" customHeight="1">
       <c r="A47" s="9"/>
@@ -1630,14 +1656,14 @@
       <c r="H51" s="9"/>
     </row>
     <row r="52" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A52" s="10"/>
-      <c r="B52" s="10"/>
-      <c r="C52" s="10"/>
-      <c r="D52" s="10"/>
-      <c r="E52" s="10"/>
-      <c r="F52" s="10"/>
-      <c r="G52" s="10"/>
-      <c r="H52" s="10"/>
+      <c r="A52" s="9"/>
+      <c r="B52" s="9"/>
+      <c r="C52" s="9"/>
+      <c r="D52" s="9"/>
+      <c r="E52" s="9"/>
+      <c r="F52" s="9"/>
+      <c r="G52" s="9"/>
+      <c r="H52" s="9"/>
     </row>
     <row r="53" spans="1:8" ht="15.75" customHeight="1">
       <c r="A53" s="10"/>
@@ -1669,7 +1695,16 @@
       <c r="G55" s="10"/>
       <c r="H55" s="10"/>
     </row>
-    <row r="56" spans="1:8" ht="15.75" customHeight="1"/>
+    <row r="56" spans="1:8" ht="15.75" customHeight="1">
+      <c r="A56" s="10"/>
+      <c r="B56" s="10"/>
+      <c r="C56" s="10"/>
+      <c r="D56" s="10"/>
+      <c r="E56" s="10"/>
+      <c r="F56" s="10"/>
+      <c r="G56" s="10"/>
+      <c r="H56" s="10"/>
+    </row>
     <row r="57" spans="1:8" ht="15.75" customHeight="1"/>
     <row r="58" spans="1:8" ht="15.75" customHeight="1"/>
     <row r="59" spans="1:8" ht="15.75" customHeight="1"/>
@@ -2634,6 +2669,7 @@
     <row r="1018" ht="15.75" customHeight="1"/>
     <row r="1019" ht="15.75" customHeight="1"/>
     <row r="1020" ht="15.75" customHeight="1"/>
+    <row r="1021" ht="15.75" customHeight="1"/>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.69972223043441772" right="0.69972223043441772" top="0.75" bottom="0.75" header="0.30000001192092896" footer="0.30000001192092896"/>

--- a/JsonConverter/ExcelFiles/0_MindDialogue.xlsx
+++ b/JsonConverter/ExcelFiles/0_MindDialogue.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\0_SonghaUnityGame\JsonConverter\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8603E63A-D824-498C-885E-F97478049B29}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE99FA39-24C8-41DC-BD7F-9F400500FBA3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="780" yWindow="780" windowWidth="27255" windowHeight="13650" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="615" yWindow="2250" windowWidth="28185" windowHeight="13950" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Table_MindDialogue" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="218" uniqueCount="167">
   <si>
     <t>CharacterDataId</t>
   </si>
@@ -366,6 +366,1934 @@
   </si>
   <si>
     <t>예상치 못한 타이밍과 잡을 수 없는 이 무력함에 밤새 울며 새벽을 보냈다. 너무 어버버 이별한 것 같다는 생각이 들었다.</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>mindDialogue_Opening_1_1_173</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>그렇게 밤을 맞이 하였고, 자야하지만 밤이 너무도 고통스럽고 외롭게 느껴졌다.</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>mindDialogue_Opening_1_1_174</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>밤새 눈물 흘리며 지치듯 잠에 들었다.</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>dateDialogue_Opening_1_1_175</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>mindDialogue_Opening_1_1_176</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>그렇게 이별 첫 날을 맞이 하게 되었다.</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>mindDialogue_Opening_1_1_177</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>아직도 실감이 나지 않았고, 아침에 일어나서도 온몸이 아프고, 눈물이 났다.</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>mindDialogue_Opening_1_1_178</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>하지만 나는 더</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>이상</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">어리지 않았고, </t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>과거의</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>나처럼</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>감정에</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>지배당하면</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>아무것도</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>변하지</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>않는다는것을</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>알고</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>있다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>.</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>mindDialogue_Opening_1_1_179</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">mindDialogue_Opening_1_1_180 </t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>mindDialogue_Opening_1_1_181</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>현재 수강하고 있는 강의를 듣기 위해 자리를 박차고 일어났다.</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>그렇게 강의를 들을 준비를 하던중 동료가 먼저 말을 걸어왔다.</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>normalDialogue_Opening_1_1_182</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>주변 사람들한테도 표가 났는지 동료가 평소와 다른 느낌이라고 말을 해주었다.</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>normalDialogue_Opening_1_1_186</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>mindDialogue_Opening_1_1_185</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>mindDialogue_Opening_1_1_187</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>다른 말없이 그 한마디에 눌러오던 감정이 터져나오듯 눈물이 쏟아졌다.</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>mindDialogue_Opening_1_1_188</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>나는 아무말도 할 수 없었고, 그 자리에서 숨죽이며 5분간 울기만 했다.</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>normalDialogue_Opening_1_1_189</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>mindDialogue_Opening_1_1_193</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>그저 남 앞에서 울기만 했지만 큰 도움이 되었고, 많은 힘이 되었다.</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>mindDialogue_Opening_1_1_194</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>그렇게 슬픔을 안은채 끝까지 수업을 들었고, 끝나자마자 근무하는 편의점으로 향했다.</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>mindDialogue_Opening_1_1_195</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>쉴틈을 주면 그녀가 속을 비집고 들어올것만 같았다.</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>mindDialogue_Opening_1_1_196</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>천천히 생각을 정리하며, 우리가 헤어져야하는 이유가 타당하고, 내가 받아 들일수 있는 이별인지 생각해보았다.</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>mindDialogue_Opening_1_1_197</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">나에게는 첫 연애이자 첫 이별이었으며, </t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>mindDialogue_Opening_1_1_198</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>정말 힘들다는 것을 몸소 느끼며 최대한 이 슬픔을 받아들이기로 했다.</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>mindDialogue_Opening_1_1_199</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>mindDialogue_Opening_1_1_200</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>하지만 알바를 하는 와중에도 그녀는 마음속에 비집고 들어왔고</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>편의점에서 나오는 노래 마저 이별 노래가 나와 더 고통스럽게 만들었다.</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>mindDialogue_Opening_1_1_201</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>그래서</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>였을까, 밤이라서 약해졌던 탓일까.</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>mindDialogue_Opening_1_1_202</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>결국 나는 알바가 끝나고 퇴근 하는 차 안에서 그녀에게 전화를 걸었다.</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>mindDialogue_Opening_1_1_203</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>통화 연결중)</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>normalDialogue_Opening_1_1_204</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>mindDialogue_Opening_1_1_222</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>사실</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>알고</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>있었다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>..</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>내가</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>잘못한것도</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>없었고</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>내가</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>못해준</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>것도</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>없었다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>.</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>단지</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>미안하다고</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>사과해야만</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>할거</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>같았기때문이다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>.</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>결혼을</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>전제라면</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>내가</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>노력할</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>수</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>있는</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>부분은</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>있지않을까하고</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>찌질하게</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>매달렸다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <t>mindDialogue_Opening_1_1_260</t>
+  </si>
+  <si>
+    <t>mindDialogue_Opening_1_1_223</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>mindDialogue_Opening_1_1_224</t>
+  </si>
+  <si>
+    <t>mindDialogue_Opening_1_1_225</t>
+  </si>
+  <si>
+    <t>mindDialogue_Opening_1_1_226</t>
+  </si>
+  <si>
+    <t>mindDialogue_Opening_1_1_224</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>mindDialogue_Opening_1_1_226</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>mindDialogue_Opening_1_1_255</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>정말로</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>명확한</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>이유를</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>알았다면</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>납득하고</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>고칠</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>수</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>있었을텐데</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>..</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>그녀는</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>끝까지</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>말하기를</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>꺼려했다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>하지만</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>한가지는</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>분명했다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>.</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>그것을</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>말한다면</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>내가</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>큰</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>상처가</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>될것이고</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>고치지도</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>변화</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>하지도</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>못하는</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>문제라고</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>말하였는데</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>나를</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>잘아는</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>그녀는</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>나에</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>대해서</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>그렇게</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>말하지</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>않을것이다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>.</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>하지만</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">.. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>이렇게까지</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>말하지</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>않는다는건</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>나를</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>지켜주려</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>했다고</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>생각한다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>.</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>그렇기</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>때문에</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>더이상</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>묻지</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>않기로</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>했다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>.</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>mindDialogue_Opening_1_1_256</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>mindDialogue_Opening_1_1_257</t>
+  </si>
+  <si>
+    <t>mindDialogue_Opening_1_1_258</t>
+  </si>
+  <si>
+    <t>mindDialogue_Opening_1_1_259</t>
+  </si>
+  <si>
+    <t>mindDialogue_Opening_1_1_261</t>
+  </si>
+  <si>
+    <t>mindDialogue_Opening_1_1_262</t>
+  </si>
+  <si>
+    <t>mindDialogue_Opening_1_1_257</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>normalDialogue_Opening_1_1_227</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>mindDialogue_Opening_1_1_262</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>normalDialogue_Opening_1_1_263</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -373,7 +2301,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
-  <fonts count="4">
+  <fonts count="9">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -395,6 +2323,39 @@
     </font>
     <font>
       <sz val="8"/>
+      <name val="돋움"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
       <name val="돋움"/>
       <family val="3"/>
       <charset val="129"/>
@@ -438,7 +2399,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -461,13 +2422,41 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -497,6 +2486,54 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1488,7 +3525,9 @@
       <c r="B35" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="C35" s="3"/>
+      <c r="C35" s="3" t="s">
+        <v>86</v>
+      </c>
       <c r="D35" s="3"/>
       <c r="E35" s="3"/>
       <c r="F35" s="3"/>
@@ -1496,9 +3535,15 @@
       <c r="H35" s="3"/>
     </row>
     <row r="36" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A36" s="3"/>
-      <c r="B36" s="3"/>
-      <c r="C36" s="3"/>
+      <c r="A36" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="C36" s="3" t="s">
+        <v>88</v>
+      </c>
       <c r="D36" s="3"/>
       <c r="E36" s="3"/>
       <c r="F36" s="3"/>
@@ -1506,9 +3551,15 @@
       <c r="H36" s="3"/>
     </row>
     <row r="37" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A37" s="8"/>
-      <c r="B37" s="8"/>
-      <c r="C37" s="8"/>
+      <c r="A37" s="11" t="s">
+        <v>88</v>
+      </c>
+      <c r="B37" s="12" t="s">
+        <v>89</v>
+      </c>
+      <c r="C37" s="11" t="s">
+        <v>90</v>
+      </c>
       <c r="D37" s="8"/>
       <c r="E37" s="8"/>
       <c r="F37" s="8"/>
@@ -1516,9 +3567,15 @@
       <c r="H37" s="8"/>
     </row>
     <row r="38" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A38" s="8"/>
-      <c r="B38" s="8"/>
-      <c r="C38" s="8"/>
+      <c r="A38" s="11" t="s">
+        <v>91</v>
+      </c>
+      <c r="B38" s="12" t="s">
+        <v>92</v>
+      </c>
+      <c r="C38" s="11" t="s">
+        <v>93</v>
+      </c>
       <c r="D38" s="8"/>
       <c r="E38" s="8"/>
       <c r="F38" s="8"/>
@@ -1526,9 +3583,15 @@
       <c r="H38" s="8"/>
     </row>
     <row r="39" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A39" s="8"/>
-      <c r="B39" s="8"/>
-      <c r="C39" s="8"/>
+      <c r="A39" s="11" t="s">
+        <v>93</v>
+      </c>
+      <c r="B39" s="13" t="s">
+        <v>94</v>
+      </c>
+      <c r="C39" s="11" t="s">
+        <v>95</v>
+      </c>
       <c r="D39" s="8"/>
       <c r="E39" s="8"/>
       <c r="F39" s="8"/>
@@ -1536,9 +3599,15 @@
       <c r="H39" s="8"/>
     </row>
     <row r="40" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A40" s="8"/>
-      <c r="B40" s="8"/>
-      <c r="C40" s="8"/>
+      <c r="A40" s="11" t="s">
+        <v>95</v>
+      </c>
+      <c r="B40" s="14" t="s">
+        <v>96</v>
+      </c>
+      <c r="C40" s="11" t="s">
+        <v>98</v>
+      </c>
       <c r="D40" s="8"/>
       <c r="E40" s="8"/>
       <c r="F40" s="8"/>
@@ -1546,9 +3615,15 @@
       <c r="H40" s="8"/>
     </row>
     <row r="41" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A41" s="8"/>
-      <c r="B41" s="8"/>
-      <c r="C41" s="8"/>
+      <c r="A41" s="11" t="s">
+        <v>98</v>
+      </c>
+      <c r="B41" s="14" t="s">
+        <v>97</v>
+      </c>
+      <c r="C41" s="11" t="s">
+        <v>99</v>
+      </c>
       <c r="D41" s="8"/>
       <c r="E41" s="8"/>
       <c r="F41" s="8"/>
@@ -1556,9 +3631,15 @@
       <c r="H41" s="8"/>
     </row>
     <row r="42" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A42" s="8"/>
-      <c r="B42" s="8"/>
-      <c r="C42" s="8"/>
+      <c r="A42" s="11" t="s">
+        <v>99</v>
+      </c>
+      <c r="B42" s="12" t="s">
+        <v>101</v>
+      </c>
+      <c r="C42" s="11" t="s">
+        <v>100</v>
+      </c>
       <c r="D42" s="8"/>
       <c r="E42" s="8"/>
       <c r="F42" s="8"/>
@@ -1566,9 +3647,15 @@
       <c r="H42" s="8"/>
     </row>
     <row r="43" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A43" s="8"/>
-      <c r="B43" s="8"/>
-      <c r="C43" s="8"/>
+      <c r="A43" s="11" t="s">
+        <v>100</v>
+      </c>
+      <c r="B43" s="12" t="s">
+        <v>102</v>
+      </c>
+      <c r="C43" s="11" t="s">
+        <v>103</v>
+      </c>
       <c r="D43" s="8"/>
       <c r="E43" s="8"/>
       <c r="F43" s="8"/>
@@ -1576,9 +3663,15 @@
       <c r="H43" s="8"/>
     </row>
     <row r="44" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A44" s="8"/>
-      <c r="B44" s="8"/>
-      <c r="C44" s="8"/>
+      <c r="A44" s="11" t="s">
+        <v>106</v>
+      </c>
+      <c r="B44" s="12" t="s">
+        <v>104</v>
+      </c>
+      <c r="C44" s="11" t="s">
+        <v>105</v>
+      </c>
       <c r="D44" s="8"/>
       <c r="E44" s="8"/>
       <c r="F44" s="8"/>
@@ -1586,9 +3679,15 @@
       <c r="H44" s="8"/>
     </row>
     <row r="45" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A45" s="8"/>
-      <c r="B45" s="8"/>
-      <c r="C45" s="8"/>
+      <c r="A45" s="11" t="s">
+        <v>107</v>
+      </c>
+      <c r="B45" s="12" t="s">
+        <v>108</v>
+      </c>
+      <c r="C45" s="11" t="s">
+        <v>109</v>
+      </c>
       <c r="D45" s="8"/>
       <c r="E45" s="8"/>
       <c r="F45" s="8"/>
@@ -1596,9 +3695,15 @@
       <c r="H45" s="8"/>
     </row>
     <row r="46" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A46" s="8"/>
-      <c r="B46" s="8"/>
-      <c r="C46" s="8"/>
+      <c r="A46" s="11" t="s">
+        <v>109</v>
+      </c>
+      <c r="B46" s="12" t="s">
+        <v>110</v>
+      </c>
+      <c r="C46" s="11" t="s">
+        <v>111</v>
+      </c>
       <c r="D46" s="8"/>
       <c r="E46" s="8"/>
       <c r="F46" s="8"/>
@@ -1606,9 +3711,15 @@
       <c r="H46" s="8"/>
     </row>
     <row r="47" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A47" s="9"/>
-      <c r="B47" s="9"/>
-      <c r="C47" s="9"/>
+      <c r="A47" s="15" t="s">
+        <v>112</v>
+      </c>
+      <c r="B47" s="16" t="s">
+        <v>113</v>
+      </c>
+      <c r="C47" s="15" t="s">
+        <v>114</v>
+      </c>
       <c r="D47" s="9"/>
       <c r="E47" s="9"/>
       <c r="F47" s="9"/>
@@ -1616,9 +3727,15 @@
       <c r="H47" s="9"/>
     </row>
     <row r="48" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A48" s="9"/>
-      <c r="B48" s="9"/>
-      <c r="C48" s="9"/>
+      <c r="A48" s="15" t="s">
+        <v>114</v>
+      </c>
+      <c r="B48" s="16" t="s">
+        <v>115</v>
+      </c>
+      <c r="C48" s="15" t="s">
+        <v>116</v>
+      </c>
       <c r="D48" s="9"/>
       <c r="E48" s="9"/>
       <c r="F48" s="9"/>
@@ -1626,9 +3743,15 @@
       <c r="H48" s="9"/>
     </row>
     <row r="49" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A49" s="9"/>
-      <c r="B49" s="9"/>
-      <c r="C49" s="9"/>
+      <c r="A49" s="15" t="s">
+        <v>116</v>
+      </c>
+      <c r="B49" s="16" t="s">
+        <v>117</v>
+      </c>
+      <c r="C49" s="15" t="s">
+        <v>118</v>
+      </c>
       <c r="D49" s="9"/>
       <c r="E49" s="9"/>
       <c r="F49" s="9"/>
@@ -1636,9 +3759,15 @@
       <c r="H49" s="9"/>
     </row>
     <row r="50" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A50" s="9"/>
-      <c r="B50" s="9"/>
-      <c r="C50" s="9"/>
+      <c r="A50" s="15" t="s">
+        <v>118</v>
+      </c>
+      <c r="B50" s="16" t="s">
+        <v>119</v>
+      </c>
+      <c r="C50" s="15" t="s">
+        <v>120</v>
+      </c>
       <c r="D50" s="9"/>
       <c r="E50" s="9"/>
       <c r="F50" s="9"/>
@@ -1646,9 +3775,15 @@
       <c r="H50" s="9"/>
     </row>
     <row r="51" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A51" s="9"/>
-      <c r="B51" s="9"/>
-      <c r="C51" s="9"/>
+      <c r="A51" s="15" t="s">
+        <v>120</v>
+      </c>
+      <c r="B51" s="16" t="s">
+        <v>121</v>
+      </c>
+      <c r="C51" s="15" t="s">
+        <v>122</v>
+      </c>
       <c r="D51" s="9"/>
       <c r="E51" s="9"/>
       <c r="F51" s="9"/>
@@ -1656,9 +3791,15 @@
       <c r="H51" s="9"/>
     </row>
     <row r="52" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A52" s="9"/>
-      <c r="B52" s="9"/>
-      <c r="C52" s="9"/>
+      <c r="A52" s="15" t="s">
+        <v>122</v>
+      </c>
+      <c r="B52" s="13" t="s">
+        <v>123</v>
+      </c>
+      <c r="C52" s="15" t="s">
+        <v>124</v>
+      </c>
       <c r="D52" s="9"/>
       <c r="E52" s="9"/>
       <c r="F52" s="9"/>
@@ -1666,9 +3807,15 @@
       <c r="H52" s="9"/>
     </row>
     <row r="53" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A53" s="10"/>
-      <c r="B53" s="10"/>
-      <c r="C53" s="10"/>
+      <c r="A53" s="17" t="s">
+        <v>124</v>
+      </c>
+      <c r="B53" s="18" t="s">
+        <v>126</v>
+      </c>
+      <c r="C53" s="17" t="s">
+        <v>125</v>
+      </c>
       <c r="D53" s="10"/>
       <c r="E53" s="10"/>
       <c r="F53" s="10"/>
@@ -1676,9 +3823,15 @@
       <c r="H53" s="10"/>
     </row>
     <row r="54" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A54" s="10"/>
-      <c r="B54" s="10"/>
-      <c r="C54" s="10"/>
+      <c r="A54" s="17" t="s">
+        <v>125</v>
+      </c>
+      <c r="B54" s="18" t="s">
+        <v>127</v>
+      </c>
+      <c r="C54" s="17" t="s">
+        <v>128</v>
+      </c>
       <c r="D54" s="10"/>
       <c r="E54" s="10"/>
       <c r="F54" s="10"/>
@@ -1686,9 +3839,15 @@
       <c r="H54" s="10"/>
     </row>
     <row r="55" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A55" s="10"/>
-      <c r="B55" s="10"/>
-      <c r="C55" s="10"/>
+      <c r="A55" s="17" t="s">
+        <v>128</v>
+      </c>
+      <c r="B55" s="19" t="s">
+        <v>129</v>
+      </c>
+      <c r="C55" s="17" t="s">
+        <v>130</v>
+      </c>
       <c r="D55" s="10"/>
       <c r="E55" s="10"/>
       <c r="F55" s="10"/>
@@ -1696,87 +3855,487 @@
       <c r="H55" s="10"/>
     </row>
     <row r="56" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A56" s="10"/>
-      <c r="B56" s="10"/>
-      <c r="C56" s="10"/>
-      <c r="D56" s="10"/>
+      <c r="A56" s="20" t="s">
+        <v>130</v>
+      </c>
+      <c r="B56" s="21" t="s">
+        <v>131</v>
+      </c>
+      <c r="C56" s="20" t="s">
+        <v>132</v>
+      </c>
+      <c r="D56" s="26"/>
       <c r="E56" s="10"/>
       <c r="F56" s="10"/>
       <c r="G56" s="10"/>
       <c r="H56" s="10"/>
     </row>
-    <row r="57" spans="1:8" ht="15.75" customHeight="1"/>
-    <row r="58" spans="1:8" ht="15.75" customHeight="1"/>
-    <row r="59" spans="1:8" ht="15.75" customHeight="1"/>
-    <row r="60" spans="1:8" ht="15.75" customHeight="1"/>
-    <row r="61" spans="1:8" ht="15.75" customHeight="1"/>
-    <row r="62" spans="1:8" ht="15.75" customHeight="1"/>
-    <row r="63" spans="1:8" ht="15.75" customHeight="1"/>
-    <row r="64" spans="1:8" ht="15.75" customHeight="1"/>
-    <row r="65" ht="15.75" customHeight="1"/>
-    <row r="66" ht="15.75" customHeight="1"/>
-    <row r="67" ht="15.75" customHeight="1"/>
-    <row r="68" ht="15.75" customHeight="1"/>
-    <row r="69" ht="15.75" customHeight="1"/>
-    <row r="70" ht="15.75" customHeight="1"/>
-    <row r="71" ht="15.75" customHeight="1"/>
-    <row r="72" ht="15.75" customHeight="1"/>
-    <row r="73" ht="15.75" customHeight="1"/>
-    <row r="74" ht="15.75" customHeight="1"/>
-    <row r="75" ht="15.75" customHeight="1"/>
-    <row r="76" ht="15.75" customHeight="1"/>
-    <row r="77" ht="15.75" customHeight="1"/>
-    <row r="78" ht="15.75" customHeight="1"/>
-    <row r="79" ht="15.75" customHeight="1"/>
-    <row r="80" ht="15.75" customHeight="1"/>
-    <row r="81" ht="15.75" customHeight="1"/>
-    <row r="82" ht="15.75" customHeight="1"/>
-    <row r="83" ht="15.75" customHeight="1"/>
-    <row r="84" ht="15.75" customHeight="1"/>
-    <row r="85" ht="15.75" customHeight="1"/>
-    <row r="86" ht="15.75" customHeight="1"/>
-    <row r="87" ht="15.75" customHeight="1"/>
-    <row r="88" ht="15.75" customHeight="1"/>
-    <row r="89" ht="15.75" customHeight="1"/>
-    <row r="90" ht="15.75" customHeight="1"/>
-    <row r="91" ht="15.75" customHeight="1"/>
-    <row r="92" ht="15.75" customHeight="1"/>
-    <row r="93" ht="15.75" customHeight="1"/>
-    <row r="94" ht="15.75" customHeight="1"/>
-    <row r="95" ht="15.75" customHeight="1"/>
-    <row r="96" ht="15.75" customHeight="1"/>
-    <row r="97" ht="15.75" customHeight="1"/>
-    <row r="98" ht="15.75" customHeight="1"/>
-    <row r="99" ht="15.75" customHeight="1"/>
-    <row r="100" ht="15.75" customHeight="1"/>
-    <row r="101" ht="15.75" customHeight="1"/>
-    <row r="102" ht="15.75" customHeight="1"/>
-    <row r="103" ht="15.75" customHeight="1"/>
-    <row r="104" ht="15.75" customHeight="1"/>
-    <row r="105" ht="15.75" customHeight="1"/>
-    <row r="106" ht="15.75" customHeight="1"/>
-    <row r="107" ht="15.75" customHeight="1"/>
-    <row r="108" ht="15.75" customHeight="1"/>
-    <row r="109" ht="15.75" customHeight="1"/>
-    <row r="110" ht="15.75" customHeight="1"/>
-    <row r="111" ht="15.75" customHeight="1"/>
-    <row r="112" ht="15.75" customHeight="1"/>
-    <row r="113" ht="15.75" customHeight="1"/>
-    <row r="114" ht="15.75" customHeight="1"/>
-    <row r="115" ht="15.75" customHeight="1"/>
-    <row r="116" ht="15.75" customHeight="1"/>
-    <row r="117" ht="15.75" customHeight="1"/>
-    <row r="118" ht="15.75" customHeight="1"/>
-    <row r="119" ht="15.75" customHeight="1"/>
-    <row r="120" ht="15.75" customHeight="1"/>
-    <row r="121" ht="15.75" customHeight="1"/>
-    <row r="122" ht="15.75" customHeight="1"/>
-    <row r="123" ht="15.75" customHeight="1"/>
-    <row r="124" ht="15.75" customHeight="1"/>
-    <row r="125" ht="15.75" customHeight="1"/>
-    <row r="126" ht="15.75" customHeight="1"/>
-    <row r="127" ht="15.75" customHeight="1"/>
-    <row r="128" ht="15.75" customHeight="1"/>
+    <row r="57" spans="1:8" ht="15.75" customHeight="1">
+      <c r="A57" s="22" t="s">
+        <v>132</v>
+      </c>
+      <c r="B57" s="22" t="s">
+        <v>133</v>
+      </c>
+      <c r="C57" s="22" t="s">
+        <v>134</v>
+      </c>
+      <c r="D57" s="23"/>
+    </row>
+    <row r="58" spans="1:8" ht="15.75" customHeight="1">
+      <c r="A58" s="22" t="s">
+        <v>135</v>
+      </c>
+      <c r="B58" s="24" t="s">
+        <v>136</v>
+      </c>
+      <c r="C58" s="22" t="s">
+        <v>142</v>
+      </c>
+      <c r="D58" s="23"/>
+    </row>
+    <row r="59" spans="1:8" ht="15.75" customHeight="1">
+      <c r="A59" s="22" t="s">
+        <v>142</v>
+      </c>
+      <c r="B59" s="25" t="s">
+        <v>137</v>
+      </c>
+      <c r="C59" s="22" t="s">
+        <v>146</v>
+      </c>
+      <c r="D59" s="23"/>
+    </row>
+    <row r="60" spans="1:8" ht="15.75" customHeight="1">
+      <c r="A60" s="22" t="s">
+        <v>143</v>
+      </c>
+      <c r="B60" s="24" t="s">
+        <v>138</v>
+      </c>
+      <c r="C60" s="22" t="s">
+        <v>144</v>
+      </c>
+      <c r="D60" s="23"/>
+    </row>
+    <row r="61" spans="1:8" ht="15.75" customHeight="1">
+      <c r="A61" s="22" t="s">
+        <v>144</v>
+      </c>
+      <c r="B61" s="24" t="s">
+        <v>139</v>
+      </c>
+      <c r="C61" s="22" t="s">
+        <v>145</v>
+      </c>
+      <c r="D61" s="23"/>
+    </row>
+    <row r="62" spans="1:8" ht="15.75" customHeight="1">
+      <c r="A62" s="22" t="s">
+        <v>147</v>
+      </c>
+      <c r="B62" s="25" t="s">
+        <v>140</v>
+      </c>
+      <c r="C62" s="22" t="s">
+        <v>164</v>
+      </c>
+      <c r="D62" s="23"/>
+    </row>
+    <row r="63" spans="1:8" ht="15.75" customHeight="1">
+      <c r="A63" s="22" t="s">
+        <v>148</v>
+      </c>
+      <c r="B63" s="24" t="s">
+        <v>149</v>
+      </c>
+      <c r="C63" s="22" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="64" spans="1:8" ht="15.75" customHeight="1">
+      <c r="A64" s="22" t="s">
+        <v>157</v>
+      </c>
+      <c r="B64" s="25" t="s">
+        <v>150</v>
+      </c>
+      <c r="C64" s="22" t="s">
+        <v>163</v>
+      </c>
+      <c r="D64" s="23"/>
+    </row>
+    <row r="65" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A65" s="22" t="s">
+        <v>158</v>
+      </c>
+      <c r="B65" s="24" t="s">
+        <v>151</v>
+      </c>
+      <c r="C65" s="22" t="s">
+        <v>159</v>
+      </c>
+      <c r="D65" s="23"/>
+    </row>
+    <row r="66" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A66" s="22" t="s">
+        <v>159</v>
+      </c>
+      <c r="B66" s="24" t="s">
+        <v>152</v>
+      </c>
+      <c r="C66" s="22" t="s">
+        <v>160</v>
+      </c>
+      <c r="D66" s="23"/>
+    </row>
+    <row r="67" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A67" s="22" t="s">
+        <v>160</v>
+      </c>
+      <c r="B67" s="25" t="s">
+        <v>153</v>
+      </c>
+      <c r="C67" s="22" t="s">
+        <v>141</v>
+      </c>
+      <c r="D67" s="23"/>
+    </row>
+    <row r="68" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A68" s="22" t="s">
+        <v>141</v>
+      </c>
+      <c r="B68" s="24" t="s">
+        <v>154</v>
+      </c>
+      <c r="C68" s="22" t="s">
+        <v>161</v>
+      </c>
+      <c r="D68" s="23"/>
+    </row>
+    <row r="69" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A69" s="22" t="s">
+        <v>161</v>
+      </c>
+      <c r="B69" s="24" t="s">
+        <v>155</v>
+      </c>
+      <c r="C69" s="22" t="s">
+        <v>162</v>
+      </c>
+      <c r="D69" s="23"/>
+    </row>
+    <row r="70" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A70" s="22" t="s">
+        <v>165</v>
+      </c>
+      <c r="B70" s="25" t="s">
+        <v>156</v>
+      </c>
+      <c r="C70" s="22" t="s">
+        <v>166</v>
+      </c>
+      <c r="D70" s="23"/>
+    </row>
+    <row r="71" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A71" s="23"/>
+      <c r="B71" s="23"/>
+      <c r="C71" s="23"/>
+      <c r="D71" s="23"/>
+    </row>
+    <row r="72" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A72" s="23"/>
+      <c r="B72" s="23"/>
+      <c r="C72" s="23"/>
+      <c r="D72" s="23"/>
+    </row>
+    <row r="73" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A73" s="23"/>
+      <c r="B73" s="23"/>
+      <c r="C73" s="23"/>
+      <c r="D73" s="23"/>
+    </row>
+    <row r="74" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A74" s="23"/>
+      <c r="B74" s="23"/>
+      <c r="C74" s="23"/>
+      <c r="D74" s="23"/>
+    </row>
+    <row r="75" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A75" s="23"/>
+      <c r="B75" s="23"/>
+      <c r="C75" s="23"/>
+      <c r="D75" s="23"/>
+    </row>
+    <row r="76" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A76" s="23"/>
+      <c r="B76" s="23"/>
+      <c r="C76" s="23"/>
+      <c r="D76" s="23"/>
+    </row>
+    <row r="77" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A77" s="23"/>
+      <c r="B77" s="23"/>
+      <c r="C77" s="23"/>
+      <c r="D77" s="23"/>
+    </row>
+    <row r="78" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A78" s="23"/>
+      <c r="B78" s="23"/>
+      <c r="C78" s="23"/>
+      <c r="D78" s="23"/>
+    </row>
+    <row r="79" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A79" s="23"/>
+      <c r="B79" s="23"/>
+      <c r="C79" s="23"/>
+      <c r="D79" s="23"/>
+    </row>
+    <row r="80" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A80" s="23"/>
+      <c r="B80" s="23"/>
+      <c r="C80" s="23"/>
+      <c r="D80" s="23"/>
+    </row>
+    <row r="81" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A81" s="23"/>
+      <c r="B81" s="23"/>
+      <c r="C81" s="23"/>
+      <c r="D81" s="23"/>
+    </row>
+    <row r="82" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A82" s="23"/>
+      <c r="B82" s="23"/>
+      <c r="C82" s="23"/>
+      <c r="D82" s="23"/>
+    </row>
+    <row r="83" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A83" s="23"/>
+      <c r="B83" s="23"/>
+      <c r="C83" s="23"/>
+      <c r="D83" s="23"/>
+    </row>
+    <row r="84" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A84" s="23"/>
+      <c r="B84" s="23"/>
+      <c r="C84" s="23"/>
+      <c r="D84" s="23"/>
+    </row>
+    <row r="85" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A85" s="23"/>
+      <c r="B85" s="23"/>
+      <c r="C85" s="23"/>
+      <c r="D85" s="23"/>
+    </row>
+    <row r="86" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A86" s="23"/>
+      <c r="B86" s="23"/>
+      <c r="C86" s="23"/>
+      <c r="D86" s="23"/>
+    </row>
+    <row r="87" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A87" s="23"/>
+      <c r="B87" s="23"/>
+      <c r="C87" s="23"/>
+      <c r="D87" s="23"/>
+    </row>
+    <row r="88" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A88" s="23"/>
+      <c r="B88" s="23"/>
+      <c r="C88" s="23"/>
+      <c r="D88" s="23"/>
+    </row>
+    <row r="89" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A89" s="23"/>
+      <c r="B89" s="23"/>
+      <c r="C89" s="23"/>
+      <c r="D89" s="23"/>
+    </row>
+    <row r="90" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A90" s="23"/>
+      <c r="B90" s="23"/>
+      <c r="C90" s="23"/>
+      <c r="D90" s="23"/>
+    </row>
+    <row r="91" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A91" s="23"/>
+      <c r="B91" s="23"/>
+      <c r="C91" s="23"/>
+      <c r="D91" s="23"/>
+    </row>
+    <row r="92" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A92" s="23"/>
+      <c r="B92" s="23"/>
+      <c r="C92" s="23"/>
+      <c r="D92" s="23"/>
+    </row>
+    <row r="93" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A93" s="23"/>
+      <c r="B93" s="23"/>
+      <c r="C93" s="23"/>
+      <c r="D93" s="23"/>
+    </row>
+    <row r="94" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A94" s="23"/>
+      <c r="B94" s="23"/>
+      <c r="C94" s="23"/>
+      <c r="D94" s="23"/>
+    </row>
+    <row r="95" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A95" s="23"/>
+      <c r="B95" s="23"/>
+      <c r="C95" s="23"/>
+      <c r="D95" s="23"/>
+    </row>
+    <row r="96" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A96" s="23"/>
+      <c r="B96" s="23"/>
+      <c r="C96" s="23"/>
+      <c r="D96" s="23"/>
+    </row>
+    <row r="97" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A97" s="23"/>
+      <c r="B97" s="23"/>
+      <c r="C97" s="23"/>
+      <c r="D97" s="23"/>
+    </row>
+    <row r="98" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A98" s="23"/>
+      <c r="B98" s="23"/>
+      <c r="C98" s="23"/>
+      <c r="D98" s="23"/>
+    </row>
+    <row r="99" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A99" s="23"/>
+      <c r="B99" s="23"/>
+      <c r="C99" s="23"/>
+      <c r="D99" s="23"/>
+    </row>
+    <row r="100" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A100" s="23"/>
+      <c r="B100" s="23"/>
+      <c r="C100" s="23"/>
+      <c r="D100" s="23"/>
+    </row>
+    <row r="101" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A101" s="23"/>
+      <c r="B101" s="23"/>
+      <c r="C101" s="23"/>
+      <c r="D101" s="23"/>
+    </row>
+    <row r="102" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A102" s="23"/>
+      <c r="B102" s="23"/>
+      <c r="C102" s="23"/>
+      <c r="D102" s="23"/>
+    </row>
+    <row r="103" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A103" s="23"/>
+      <c r="B103" s="23"/>
+      <c r="C103" s="23"/>
+      <c r="D103" s="23"/>
+    </row>
+    <row r="104" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A104" s="23"/>
+      <c r="B104" s="23"/>
+      <c r="C104" s="23"/>
+    </row>
+    <row r="105" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A105" s="23"/>
+      <c r="B105" s="23"/>
+      <c r="C105" s="23"/>
+    </row>
+    <row r="106" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A106" s="23"/>
+      <c r="B106" s="23"/>
+      <c r="C106" s="23"/>
+    </row>
+    <row r="107" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A107" s="23"/>
+      <c r="B107" s="23"/>
+      <c r="C107" s="23"/>
+    </row>
+    <row r="108" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A108" s="23"/>
+      <c r="B108" s="23"/>
+      <c r="C108" s="23"/>
+    </row>
+    <row r="109" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A109" s="23"/>
+      <c r="B109" s="23"/>
+      <c r="C109" s="23"/>
+    </row>
+    <row r="110" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A110" s="23"/>
+      <c r="B110" s="23"/>
+      <c r="C110" s="23"/>
+    </row>
+    <row r="111" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A111" s="23"/>
+      <c r="B111" s="23"/>
+      <c r="C111" s="23"/>
+    </row>
+    <row r="112" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A112" s="23"/>
+      <c r="B112" s="23"/>
+      <c r="C112" s="23"/>
+    </row>
+    <row r="113" spans="1:3" ht="15.75" customHeight="1">
+      <c r="A113" s="23"/>
+      <c r="B113" s="23"/>
+      <c r="C113" s="23"/>
+    </row>
+    <row r="114" spans="1:3" ht="15.75" customHeight="1">
+      <c r="A114" s="23"/>
+      <c r="B114" s="23"/>
+      <c r="C114" s="23"/>
+    </row>
+    <row r="115" spans="1:3" ht="15.75" customHeight="1">
+      <c r="A115" s="23"/>
+      <c r="B115" s="23"/>
+      <c r="C115" s="23"/>
+    </row>
+    <row r="116" spans="1:3" ht="15.75" customHeight="1">
+      <c r="A116" s="23"/>
+      <c r="B116" s="23"/>
+      <c r="C116" s="23"/>
+    </row>
+    <row r="117" spans="1:3" ht="15.75" customHeight="1">
+      <c r="A117" s="23"/>
+      <c r="B117" s="23"/>
+      <c r="C117" s="23"/>
+    </row>
+    <row r="118" spans="1:3" ht="15.75" customHeight="1">
+      <c r="A118" s="23"/>
+      <c r="B118" s="23"/>
+      <c r="C118" s="23"/>
+    </row>
+    <row r="119" spans="1:3" ht="15.75" customHeight="1">
+      <c r="A119" s="23"/>
+      <c r="B119" s="23"/>
+      <c r="C119" s="23"/>
+    </row>
+    <row r="120" spans="1:3" ht="15.75" customHeight="1">
+      <c r="A120" s="23"/>
+      <c r="B120" s="23"/>
+      <c r="C120" s="23"/>
+    </row>
+    <row r="121" spans="1:3" ht="15.75" customHeight="1">
+      <c r="A121" s="23"/>
+      <c r="B121" s="23"/>
+      <c r="C121" s="23"/>
+    </row>
+    <row r="122" spans="1:3" ht="15.75" customHeight="1">
+      <c r="A122" s="23"/>
+      <c r="B122" s="23"/>
+      <c r="C122" s="23"/>
+    </row>
+    <row r="123" spans="1:3" ht="15.75" customHeight="1"/>
+    <row r="124" spans="1:3" ht="15.75" customHeight="1"/>
+    <row r="125" spans="1:3" ht="15.75" customHeight="1"/>
+    <row r="126" spans="1:3" ht="15.75" customHeight="1"/>
+    <row r="127" spans="1:3" ht="15.75" customHeight="1"/>
+    <row r="128" spans="1:3" ht="15.75" customHeight="1"/>
     <row r="129" ht="15.75" customHeight="1"/>
     <row r="130" ht="15.75" customHeight="1"/>
     <row r="131" ht="15.75" customHeight="1"/>

--- a/JsonConverter/ExcelFiles/0_MindDialogue.xlsx
+++ b/JsonConverter/ExcelFiles/0_MindDialogue.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\0_SonghaUnityGame\JsonConverter\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8603E63A-D824-498C-885E-F97478049B29}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A8403DAC-1E6F-4971-8D2F-531DEE02B6D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="780" yWindow="780" windowWidth="27255" windowHeight="13650" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="360" yWindow="960" windowWidth="28185" windowHeight="14490" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Table_MindDialogue" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="286" uniqueCount="186">
   <si>
     <t>CharacterDataId</t>
   </si>
@@ -318,10 +318,6 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>mindDialogue_Opening_1_1_162</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>normalDialogue_Opening_1_1_147</t>
   </si>
   <si>
@@ -366,6 +362,2001 @@
   </si>
   <si>
     <t>예상치 못한 타이밍과 잡을 수 없는 이 무력함에 밤새 울며 새벽을 보냈다. 너무 어버버 이별한 것 같다는 생각이 들었다.</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>mindDialogue_Opening_1_1_173</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>그렇게 밤을 맞이 하였고, 자야하지만 밤이 너무도 고통스럽고 외롭게 느껴졌다.</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>mindDialogue_Opening_1_1_174</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>밤새 눈물 흘리며 지치듯 잠에 들었다.</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>dateDialogue_Opening_1_1_175</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>mindDialogue_Opening_1_1_176</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>그렇게 이별 첫 날을 맞이 하게 되었다.</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>mindDialogue_Opening_1_1_177</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>아직도 실감이 나지 않았고, 아침에 일어나서도 온몸이 아프고, 눈물이 났다.</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>mindDialogue_Opening_1_1_178</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>하지만 나는 더</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>이상</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">어리지 않았고, </t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>과거의</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>나처럼</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>감정에</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>지배당하면</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>아무것도</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>변하지</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>않는다는것을</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>알고</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>있다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>.</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>mindDialogue_Opening_1_1_179</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">mindDialogue_Opening_1_1_180 </t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>mindDialogue_Opening_1_1_181</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>현재 수강하고 있는 강의를 듣기 위해 자리를 박차고 일어났다.</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>그렇게 강의를 들을 준비를 하던중 동료가 먼저 말을 걸어왔다.</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>normalDialogue_Opening_1_1_182</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>주변 사람들한테도 표가 났는지 동료가 평소와 다른 느낌이라고 말을 해주었다.</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>normalDialogue_Opening_1_1_186</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>mindDialogue_Opening_1_1_185</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>mindDialogue_Opening_1_1_187</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>다른 말없이 그 한마디에 눌러오던 감정이 터져나오듯 눈물이 쏟아졌다.</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>mindDialogue_Opening_1_1_188</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>나는 아무말도 할 수 없었고, 그 자리에서 숨죽이며 5분간 울기만 했다.</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>normalDialogue_Opening_1_1_189</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>mindDialogue_Opening_1_1_193</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>그저 남 앞에서 울기만 했지만 큰 도움이 되었고, 많은 힘이 되었다.</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>mindDialogue_Opening_1_1_194</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>그렇게 슬픔을 안은채 끝까지 수업을 들었고, 끝나자마자 근무하는 편의점으로 향했다.</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>mindDialogue_Opening_1_1_195</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>쉴틈을 주면 그녀가 속을 비집고 들어올것만 같았다.</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>mindDialogue_Opening_1_1_196</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>천천히 생각을 정리하며, 우리가 헤어져야하는 이유가 타당하고, 내가 받아 들일수 있는 이별인지 생각해보았다.</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>mindDialogue_Opening_1_1_197</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">나에게는 첫 연애이자 첫 이별이었으며, </t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>mindDialogue_Opening_1_1_198</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>정말 힘들다는 것을 몸소 느끼며 최대한 이 슬픔을 받아들이기로 했다.</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>mindDialogue_Opening_1_1_199</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>mindDialogue_Opening_1_1_200</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>하지만 알바를 하는 와중에도 그녀는 마음속에 비집고 들어왔고</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>편의점에서 나오는 노래 마저 이별 노래가 나와 더 고통스럽게 만들었다.</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>mindDialogue_Opening_1_1_201</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>그래서</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>였을까, 밤이라서 약해졌던 탓일까.</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>mindDialogue_Opening_1_1_202</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>결국 나는 알바가 끝나고 퇴근 하는 차 안에서 그녀에게 전화를 걸었다.</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>mindDialogue_Opening_1_1_203</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>통화 연결중)</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>normalDialogue_Opening_1_1_204</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>mindDialogue_Opening_1_1_222</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>사실</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>알고</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>있었다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>..</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>내가</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>잘못한것도</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>없었고</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>내가</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>못해준</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>것도</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>없었다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>.</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>단지</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>미안하다고</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>사과해야만</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>할거</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>같았기때문이다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>.</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>결혼을</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>전제라면</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>내가</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>노력할</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>수</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>있는</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>부분은</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>있지않을까하고</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>찌질하게</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>매달렸다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <t>mindDialogue_Opening_1_1_260</t>
+  </si>
+  <si>
+    <t>mindDialogue_Opening_1_1_223</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>mindDialogue_Opening_1_1_224</t>
+  </si>
+  <si>
+    <t>mindDialogue_Opening_1_1_225</t>
+  </si>
+  <si>
+    <t>mindDialogue_Opening_1_1_226</t>
+  </si>
+  <si>
+    <t>mindDialogue_Opening_1_1_224</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>mindDialogue_Opening_1_1_226</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>mindDialogue_Opening_1_1_255</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>정말로</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>명확한</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>이유를</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>알았다면</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>납득하고</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>고칠</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>수</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>있었을텐데</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>..</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>그녀는</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>끝까지</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>말하기를</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>꺼려했다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>하지만</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>한가지는</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>분명했다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>.</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>그것을</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>말한다면</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>내가</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>큰</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>상처가</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>될것이고</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>고치지도</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>변화</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>하지도</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>못하는</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>문제라고</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>말하였는데</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>나를</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>잘아는</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>그녀는</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>나에</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>대해서</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>그렇게</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>말하지</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>않을것이다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>.</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>하지만</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">.. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>이렇게까지</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>말하지</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>않는다는건</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>나를</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>지켜주려</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>했다고</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>생각한다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>.</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>그렇기</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>때문에</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>더이상</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>묻지</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>않기로</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>했다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>.</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>mindDialogue_Opening_1_1_256</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>mindDialogue_Opening_1_1_257</t>
+  </si>
+  <si>
+    <t>mindDialogue_Opening_1_1_258</t>
+  </si>
+  <si>
+    <t>mindDialogue_Opening_1_1_259</t>
+  </si>
+  <si>
+    <t>mindDialogue_Opening_1_1_261</t>
+  </si>
+  <si>
+    <t>mindDialogue_Opening_1_1_262</t>
+  </si>
+  <si>
+    <t>mindDialogue_Opening_1_1_257</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>normalDialogue_Opening_1_1_227</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>mindDialogue_Opening_1_1_262</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>normalDialogue_Opening_1_1_263</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>BGImagePath</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Sprite/Call Image</t>
+  </si>
+  <si>
+    <t>Sprite/Before Sleep</t>
+  </si>
+  <si>
+    <t>Sprite/Call Army</t>
+  </si>
+  <si>
+    <t>Sprite/Call Image</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Sprite/Before Sleep Empty</t>
+  </si>
+  <si>
+    <t>Sprite/Photo amusemenpark</t>
+  </si>
+  <si>
+    <t>Sprite/Before Sleep Empty</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Sprite/Dark empty Room</t>
+  </si>
+  <si>
+    <t>Sprite/Before Sleep</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Sprite/morning empty Room</t>
+  </si>
+  <si>
+    <t>Sprite/Out Class cry</t>
+  </si>
+  <si>
+    <t>Sprite/Class Room study.</t>
+  </si>
+  <si>
+    <t>Sprite/CU work</t>
+  </si>
+  <si>
+    <t>Sprite/CU cry</t>
+  </si>
+  <si>
+    <t>Sprite/CU work</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Sprite/Cu go home</t>
+  </si>
+  <si>
+    <t>Sprite/CU go home cry</t>
+  </si>
+  <si>
+    <t>Sprite/Class Room</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Sprite/Out Class cry</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -373,7 +2364,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
-  <fonts count="4">
+  <fonts count="9">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -395,6 +2386,39 @@
     </font>
     <font>
       <sz val="8"/>
+      <name val="돋움"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
       <name val="돋움"/>
       <family val="3"/>
       <charset val="129"/>
@@ -438,7 +2462,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -461,13 +2485,41 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -497,6 +2549,57 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -971,7 +3074,9 @@
       <c r="C3" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="D3" s="6"/>
+      <c r="D3" s="6" t="s">
+        <v>166</v>
+      </c>
       <c r="E3" s="6" t="s">
         <v>2</v>
       </c>
@@ -995,6 +3100,9 @@
       <c r="C4" s="1" t="s">
         <v>15</v>
       </c>
+      <c r="D4" s="27" t="s">
+        <v>175</v>
+      </c>
       <c r="F4" s="1" t="s">
         <v>10</v>
       </c>
@@ -1011,7 +3119,9 @@
       <c r="C5" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="D5" s="1"/>
+      <c r="D5" s="1" t="s">
+        <v>175</v>
+      </c>
       <c r="E5" s="1"/>
       <c r="F5" s="1"/>
       <c r="G5" s="1"/>
@@ -1027,7 +3137,9 @@
       <c r="C6" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="D6" s="1"/>
+      <c r="D6" s="1" t="s">
+        <v>168</v>
+      </c>
       <c r="E6" s="1"/>
       <c r="F6" s="1"/>
       <c r="G6" s="1"/>
@@ -1043,7 +3155,9 @@
       <c r="C7" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="D7" s="1"/>
+      <c r="D7" s="1" t="s">
+        <v>168</v>
+      </c>
       <c r="E7" s="1"/>
       <c r="F7" s="1"/>
       <c r="G7" s="1"/>
@@ -1059,7 +3173,9 @@
       <c r="C8" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="D8" s="1"/>
+      <c r="D8" s="1" t="s">
+        <v>168</v>
+      </c>
       <c r="E8" s="1"/>
       <c r="F8" s="1"/>
       <c r="G8" s="1"/>
@@ -1075,7 +3191,9 @@
       <c r="C9" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="D9" s="1"/>
+      <c r="D9" s="1" t="s">
+        <v>167</v>
+      </c>
       <c r="E9" s="1"/>
       <c r="F9" s="1"/>
       <c r="G9" s="1"/>
@@ -1091,7 +3209,9 @@
       <c r="C10" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="D10" s="1"/>
+      <c r="D10" s="1" t="s">
+        <v>170</v>
+      </c>
       <c r="E10" s="1"/>
       <c r="F10" s="1"/>
       <c r="G10" s="1"/>
@@ -1107,7 +3227,9 @@
       <c r="C11" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="D11" s="1"/>
+      <c r="D11" s="1" t="s">
+        <v>170</v>
+      </c>
       <c r="E11" s="1"/>
       <c r="F11" s="1"/>
       <c r="G11" s="1"/>
@@ -1123,7 +3245,9 @@
       <c r="C12" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D12" s="1"/>
+      <c r="D12" s="1" t="s">
+        <v>169</v>
+      </c>
       <c r="E12" s="1"/>
       <c r="F12" s="1"/>
       <c r="G12" s="1"/>
@@ -1139,7 +3263,9 @@
       <c r="C13" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D13" s="1"/>
+      <c r="D13" s="1" t="s">
+        <v>169</v>
+      </c>
       <c r="E13" s="1"/>
       <c r="F13" s="1"/>
       <c r="G13" s="1"/>
@@ -1155,7 +3281,9 @@
       <c r="C14" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="D14" s="1"/>
+      <c r="D14" s="1" t="s">
+        <v>169</v>
+      </c>
       <c r="E14" s="1"/>
       <c r="F14" s="1"/>
       <c r="G14" s="1"/>
@@ -1166,12 +3294,14 @@
         <v>39</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="D15" s="1"/>
+        <v>78</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>169</v>
+      </c>
       <c r="E15" s="1"/>
       <c r="F15" s="1"/>
       <c r="G15" s="1"/>
@@ -1179,15 +3309,17 @@
     </row>
     <row r="16" spans="1:8" ht="15.75" customHeight="1">
       <c r="A16" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="B16" s="1" t="s">
         <v>79</v>
-      </c>
-      <c r="B16" s="1" t="s">
-        <v>80</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D16" s="1"/>
+      <c r="D16" s="1" t="s">
+        <v>169</v>
+      </c>
       <c r="E16" s="1"/>
       <c r="F16" s="1"/>
       <c r="G16" s="1"/>
@@ -1198,12 +3330,14 @@
         <v>40</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="D17" s="1"/>
+      <c r="D17" s="1" t="s">
+        <v>169</v>
+      </c>
       <c r="E17" s="1"/>
       <c r="F17" s="1"/>
       <c r="G17" s="1"/>
@@ -1219,7 +3353,9 @@
       <c r="C18" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="D18" s="1"/>
+      <c r="D18" s="1" t="s">
+        <v>169</v>
+      </c>
       <c r="E18" s="1"/>
       <c r="F18" s="1"/>
       <c r="G18" s="1"/>
@@ -1235,7 +3371,9 @@
       <c r="C19" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="D19" s="2"/>
+      <c r="D19" s="2" t="s">
+        <v>171</v>
+      </c>
       <c r="E19" s="2"/>
       <c r="F19" s="2"/>
       <c r="G19" s="2"/>
@@ -1251,7 +3389,9 @@
       <c r="C20" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="D20" s="2"/>
+      <c r="D20" s="2" t="s">
+        <v>173</v>
+      </c>
       <c r="E20" s="2"/>
       <c r="F20" s="2"/>
       <c r="G20" s="2"/>
@@ -1267,7 +3407,9 @@
       <c r="C21" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="D21" s="2"/>
+      <c r="D21" s="2" t="s">
+        <v>171</v>
+      </c>
       <c r="E21" s="2"/>
       <c r="F21" s="2"/>
       <c r="G21" s="2"/>
@@ -1283,7 +3425,9 @@
       <c r="C22" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="D22" s="2"/>
+      <c r="D22" s="2" t="s">
+        <v>171</v>
+      </c>
       <c r="E22" s="2"/>
       <c r="F22" s="2"/>
       <c r="G22" s="2"/>
@@ -1299,7 +3443,9 @@
       <c r="C23" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="D23" s="2"/>
+      <c r="D23" s="2" t="s">
+        <v>167</v>
+      </c>
       <c r="E23" s="2"/>
       <c r="F23" s="2"/>
       <c r="G23" s="1"/>
@@ -1315,7 +3461,9 @@
       <c r="C24" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="D24" s="2"/>
+      <c r="D24" s="2" t="s">
+        <v>170</v>
+      </c>
       <c r="E24" s="2"/>
       <c r="F24" s="2"/>
       <c r="G24" s="1"/>
@@ -1331,7 +3479,9 @@
       <c r="C25" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="D25" s="3"/>
+      <c r="D25" s="3" t="s">
+        <v>172</v>
+      </c>
       <c r="E25" s="3"/>
       <c r="F25" s="3"/>
       <c r="G25" s="3"/>
@@ -1347,7 +3497,9 @@
       <c r="C26" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="D26" s="3"/>
+      <c r="D26" s="3" t="s">
+        <v>172</v>
+      </c>
       <c r="E26" s="3"/>
       <c r="F26" s="3"/>
       <c r="G26" s="3"/>
@@ -1361,9 +3513,11 @@
         <v>60</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="D27" s="3"/>
+        <v>73</v>
+      </c>
+      <c r="D27" s="3" t="s">
+        <v>172</v>
+      </c>
       <c r="E27" s="3"/>
       <c r="F27" s="3"/>
       <c r="G27" s="3"/>
@@ -1374,12 +3528,14 @@
         <v>62</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C28" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="D28" s="3"/>
+      <c r="D28" s="3" t="s">
+        <v>170</v>
+      </c>
       <c r="E28" s="3"/>
       <c r="F28" s="3"/>
       <c r="G28" s="3"/>
@@ -1395,7 +3551,9 @@
       <c r="C29" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="D29" s="3"/>
+      <c r="D29" s="3" t="s">
+        <v>170</v>
+      </c>
       <c r="E29" s="3"/>
       <c r="F29" s="3"/>
       <c r="G29" s="3"/>
@@ -1411,7 +3569,9 @@
       <c r="C30" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="D30" s="3"/>
+      <c r="D30" s="3" t="s">
+        <v>167</v>
+      </c>
       <c r="E30" s="3"/>
       <c r="F30" s="3"/>
       <c r="G30" s="3"/>
@@ -1425,9 +3585,11 @@
         <v>68</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="D31" s="3"/>
+        <v>81</v>
+      </c>
+      <c r="D31" s="3" t="s">
+        <v>167</v>
+      </c>
       <c r="E31" s="3"/>
       <c r="F31" s="3"/>
       <c r="G31" s="3"/>
@@ -1441,9 +3603,11 @@
         <v>72</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="D32" s="2"/>
+        <v>70</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>171</v>
+      </c>
       <c r="E32" s="2"/>
       <c r="F32" s="2"/>
       <c r="G32" s="2"/>
@@ -1457,9 +3621,11 @@
         <v>71</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="D33" s="2"/>
+        <v>74</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>173</v>
+      </c>
       <c r="E33" s="2"/>
       <c r="F33" s="2"/>
       <c r="G33" s="2"/>
@@ -1467,15 +3633,17 @@
     </row>
     <row r="34" spans="1:8" ht="15.75" customHeight="1">
       <c r="A34" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B34" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="C34" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="C34" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="D34" s="1"/>
+      <c r="D34" s="1" t="s">
+        <v>171</v>
+      </c>
       <c r="E34" s="1"/>
       <c r="F34" s="1"/>
       <c r="G34" s="1"/>
@@ -1483,300 +3651,895 @@
     </row>
     <row r="35" spans="1:8" ht="15.75" customHeight="1">
       <c r="A35" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="B35" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="B35" s="3" t="s">
+      <c r="C35" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="C35" s="3"/>
-      <c r="D35" s="3"/>
+      <c r="D35" s="3" t="s">
+        <v>171</v>
+      </c>
       <c r="E35" s="3"/>
       <c r="F35" s="3"/>
       <c r="G35" s="3"/>
       <c r="H35" s="3"/>
     </row>
     <row r="36" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A36" s="3"/>
-      <c r="B36" s="3"/>
-      <c r="C36" s="3"/>
-      <c r="D36" s="3"/>
+      <c r="A36" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="C36" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="D36" s="3" t="s">
+        <v>171</v>
+      </c>
       <c r="E36" s="3"/>
       <c r="F36" s="3"/>
       <c r="G36" s="3"/>
       <c r="H36" s="3"/>
     </row>
     <row r="37" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A37" s="8"/>
-      <c r="B37" s="8"/>
-      <c r="C37" s="8"/>
-      <c r="D37" s="8"/>
+      <c r="A37" s="11" t="s">
+        <v>87</v>
+      </c>
+      <c r="B37" s="12" t="s">
+        <v>88</v>
+      </c>
+      <c r="C37" s="11" t="s">
+        <v>89</v>
+      </c>
+      <c r="D37" s="8" t="s">
+        <v>174</v>
+      </c>
       <c r="E37" s="8"/>
       <c r="F37" s="8"/>
       <c r="G37" s="8"/>
       <c r="H37" s="8"/>
     </row>
     <row r="38" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A38" s="8"/>
-      <c r="B38" s="8"/>
-      <c r="C38" s="8"/>
-      <c r="D38" s="8"/>
+      <c r="A38" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="B38" s="12" t="s">
+        <v>91</v>
+      </c>
+      <c r="C38" s="11" t="s">
+        <v>92</v>
+      </c>
+      <c r="D38" s="8" t="s">
+        <v>174</v>
+      </c>
       <c r="E38" s="8"/>
       <c r="F38" s="8"/>
       <c r="G38" s="8"/>
       <c r="H38" s="8"/>
     </row>
     <row r="39" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A39" s="8"/>
-      <c r="B39" s="8"/>
-      <c r="C39" s="8"/>
-      <c r="D39" s="8"/>
+      <c r="A39" s="11" t="s">
+        <v>92</v>
+      </c>
+      <c r="B39" s="13" t="s">
+        <v>93</v>
+      </c>
+      <c r="C39" s="11" t="s">
+        <v>94</v>
+      </c>
+      <c r="D39" s="8" t="s">
+        <v>176</v>
+      </c>
       <c r="E39" s="8"/>
       <c r="F39" s="8"/>
       <c r="G39" s="8"/>
       <c r="H39" s="8"/>
     </row>
     <row r="40" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A40" s="8"/>
-      <c r="B40" s="8"/>
-      <c r="C40" s="8"/>
-      <c r="D40" s="8"/>
+      <c r="A40" s="11" t="s">
+        <v>94</v>
+      </c>
+      <c r="B40" s="14" t="s">
+        <v>95</v>
+      </c>
+      <c r="C40" s="11" t="s">
+        <v>97</v>
+      </c>
+      <c r="D40" s="8" t="s">
+        <v>176</v>
+      </c>
       <c r="E40" s="8"/>
       <c r="F40" s="8"/>
       <c r="G40" s="8"/>
       <c r="H40" s="8"/>
     </row>
     <row r="41" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A41" s="8"/>
-      <c r="B41" s="8"/>
-      <c r="C41" s="8"/>
-      <c r="D41" s="8"/>
+      <c r="A41" s="11" t="s">
+        <v>97</v>
+      </c>
+      <c r="B41" s="14" t="s">
+        <v>96</v>
+      </c>
+      <c r="C41" s="11" t="s">
+        <v>98</v>
+      </c>
+      <c r="D41" s="8" t="s">
+        <v>176</v>
+      </c>
       <c r="E41" s="8"/>
       <c r="F41" s="8"/>
       <c r="G41" s="8"/>
       <c r="H41" s="8"/>
     </row>
     <row r="42" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A42" s="8"/>
-      <c r="B42" s="8"/>
-      <c r="C42" s="8"/>
-      <c r="D42" s="8"/>
+      <c r="A42" s="11" t="s">
+        <v>98</v>
+      </c>
+      <c r="B42" s="12" t="s">
+        <v>100</v>
+      </c>
+      <c r="C42" s="11" t="s">
+        <v>99</v>
+      </c>
+      <c r="D42" s="8" t="s">
+        <v>176</v>
+      </c>
       <c r="E42" s="8"/>
       <c r="F42" s="8"/>
       <c r="G42" s="8"/>
       <c r="H42" s="8"/>
     </row>
     <row r="43" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A43" s="8"/>
-      <c r="B43" s="8"/>
-      <c r="C43" s="8"/>
-      <c r="D43" s="8"/>
+      <c r="A43" s="11" t="s">
+        <v>99</v>
+      </c>
+      <c r="B43" s="12" t="s">
+        <v>101</v>
+      </c>
+      <c r="C43" s="11" t="s">
+        <v>102</v>
+      </c>
+      <c r="D43" s="11" t="s">
+        <v>184</v>
+      </c>
       <c r="E43" s="8"/>
       <c r="F43" s="8"/>
       <c r="G43" s="8"/>
       <c r="H43" s="8"/>
     </row>
     <row r="44" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A44" s="8"/>
-      <c r="B44" s="8"/>
-      <c r="C44" s="8"/>
-      <c r="D44" s="8"/>
+      <c r="A44" s="11" t="s">
+        <v>105</v>
+      </c>
+      <c r="B44" s="12" t="s">
+        <v>103</v>
+      </c>
+      <c r="C44" s="11" t="s">
+        <v>104</v>
+      </c>
+      <c r="D44" s="11" t="s">
+        <v>185</v>
+      </c>
       <c r="E44" s="8"/>
       <c r="F44" s="8"/>
       <c r="G44" s="8"/>
       <c r="H44" s="8"/>
     </row>
     <row r="45" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A45" s="8"/>
-      <c r="B45" s="8"/>
-      <c r="C45" s="8"/>
-      <c r="D45" s="8"/>
+      <c r="A45" s="11" t="s">
+        <v>106</v>
+      </c>
+      <c r="B45" s="12" t="s">
+        <v>107</v>
+      </c>
+      <c r="C45" s="11" t="s">
+        <v>108</v>
+      </c>
+      <c r="D45" s="11" t="s">
+        <v>185</v>
+      </c>
       <c r="E45" s="8"/>
       <c r="F45" s="8"/>
       <c r="G45" s="8"/>
       <c r="H45" s="8"/>
     </row>
     <row r="46" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A46" s="8"/>
-      <c r="B46" s="8"/>
-      <c r="C46" s="8"/>
-      <c r="D46" s="8"/>
+      <c r="A46" s="11" t="s">
+        <v>108</v>
+      </c>
+      <c r="B46" s="12" t="s">
+        <v>109</v>
+      </c>
+      <c r="C46" s="11" t="s">
+        <v>110</v>
+      </c>
+      <c r="D46" s="8" t="s">
+        <v>177</v>
+      </c>
       <c r="E46" s="8"/>
       <c r="F46" s="8"/>
       <c r="G46" s="8"/>
       <c r="H46" s="8"/>
     </row>
     <row r="47" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A47" s="9"/>
-      <c r="B47" s="9"/>
-      <c r="C47" s="9"/>
-      <c r="D47" s="9"/>
+      <c r="A47" s="15" t="s">
+        <v>111</v>
+      </c>
+      <c r="B47" s="16" t="s">
+        <v>112</v>
+      </c>
+      <c r="C47" s="15" t="s">
+        <v>113</v>
+      </c>
+      <c r="D47" s="9" t="s">
+        <v>178</v>
+      </c>
       <c r="E47" s="9"/>
       <c r="F47" s="9"/>
       <c r="G47" s="9"/>
       <c r="H47" s="9"/>
     </row>
     <row r="48" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A48" s="9"/>
-      <c r="B48" s="9"/>
-      <c r="C48" s="9"/>
-      <c r="D48" s="9"/>
+      <c r="A48" s="15" t="s">
+        <v>113</v>
+      </c>
+      <c r="B48" s="16" t="s">
+        <v>114</v>
+      </c>
+      <c r="C48" s="15" t="s">
+        <v>115</v>
+      </c>
+      <c r="D48" s="9" t="s">
+        <v>178</v>
+      </c>
       <c r="E48" s="9"/>
       <c r="F48" s="9"/>
       <c r="G48" s="9"/>
       <c r="H48" s="9"/>
     </row>
     <row r="49" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A49" s="9"/>
-      <c r="B49" s="9"/>
-      <c r="C49" s="9"/>
-      <c r="D49" s="9"/>
+      <c r="A49" s="15" t="s">
+        <v>115</v>
+      </c>
+      <c r="B49" s="16" t="s">
+        <v>116</v>
+      </c>
+      <c r="C49" s="15" t="s">
+        <v>117</v>
+      </c>
+      <c r="D49" s="9" t="s">
+        <v>179</v>
+      </c>
       <c r="E49" s="9"/>
       <c r="F49" s="9"/>
       <c r="G49" s="9"/>
       <c r="H49" s="9"/>
     </row>
     <row r="50" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A50" s="9"/>
-      <c r="B50" s="9"/>
-      <c r="C50" s="9"/>
-      <c r="D50" s="9"/>
+      <c r="A50" s="15" t="s">
+        <v>117</v>
+      </c>
+      <c r="B50" s="16" t="s">
+        <v>118</v>
+      </c>
+      <c r="C50" s="15" t="s">
+        <v>119</v>
+      </c>
+      <c r="D50" s="9" t="s">
+        <v>179</v>
+      </c>
       <c r="E50" s="9"/>
       <c r="F50" s="9"/>
       <c r="G50" s="9"/>
       <c r="H50" s="9"/>
     </row>
     <row r="51" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A51" s="9"/>
-      <c r="B51" s="9"/>
-      <c r="C51" s="9"/>
-      <c r="D51" s="9"/>
+      <c r="A51" s="15" t="s">
+        <v>119</v>
+      </c>
+      <c r="B51" s="16" t="s">
+        <v>120</v>
+      </c>
+      <c r="C51" s="15" t="s">
+        <v>121</v>
+      </c>
+      <c r="D51" s="9" t="s">
+        <v>179</v>
+      </c>
       <c r="E51" s="9"/>
       <c r="F51" s="9"/>
       <c r="G51" s="9"/>
       <c r="H51" s="9"/>
     </row>
     <row r="52" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A52" s="9"/>
-      <c r="B52" s="9"/>
-      <c r="C52" s="9"/>
-      <c r="D52" s="9"/>
+      <c r="A52" s="15" t="s">
+        <v>121</v>
+      </c>
+      <c r="B52" s="13" t="s">
+        <v>122</v>
+      </c>
+      <c r="C52" s="15" t="s">
+        <v>123</v>
+      </c>
+      <c r="D52" s="9" t="s">
+        <v>179</v>
+      </c>
       <c r="E52" s="9"/>
       <c r="F52" s="9"/>
       <c r="G52" s="9"/>
       <c r="H52" s="9"/>
     </row>
     <row r="53" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A53" s="10"/>
-      <c r="B53" s="10"/>
-      <c r="C53" s="10"/>
-      <c r="D53" s="10"/>
+      <c r="A53" s="17" t="s">
+        <v>123</v>
+      </c>
+      <c r="B53" s="18" t="s">
+        <v>125</v>
+      </c>
+      <c r="C53" s="17" t="s">
+        <v>124</v>
+      </c>
+      <c r="D53" s="17" t="s">
+        <v>181</v>
+      </c>
       <c r="E53" s="10"/>
       <c r="F53" s="10"/>
       <c r="G53" s="10"/>
       <c r="H53" s="10"/>
     </row>
     <row r="54" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A54" s="10"/>
-      <c r="B54" s="10"/>
-      <c r="C54" s="10"/>
-      <c r="D54" s="10"/>
+      <c r="A54" s="17" t="s">
+        <v>124</v>
+      </c>
+      <c r="B54" s="18" t="s">
+        <v>126</v>
+      </c>
+      <c r="C54" s="17" t="s">
+        <v>127</v>
+      </c>
+      <c r="D54" s="10" t="s">
+        <v>180</v>
+      </c>
       <c r="E54" s="10"/>
       <c r="F54" s="10"/>
       <c r="G54" s="10"/>
       <c r="H54" s="10"/>
     </row>
     <row r="55" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A55" s="10"/>
-      <c r="B55" s="10"/>
-      <c r="C55" s="10"/>
-      <c r="D55" s="10"/>
+      <c r="A55" s="17" t="s">
+        <v>127</v>
+      </c>
+      <c r="B55" s="19" t="s">
+        <v>128</v>
+      </c>
+      <c r="C55" s="17" t="s">
+        <v>129</v>
+      </c>
+      <c r="D55" s="10" t="s">
+        <v>180</v>
+      </c>
       <c r="E55" s="10"/>
       <c r="F55" s="10"/>
       <c r="G55" s="10"/>
       <c r="H55" s="10"/>
     </row>
     <row r="56" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A56" s="10"/>
-      <c r="B56" s="10"/>
-      <c r="C56" s="10"/>
-      <c r="D56" s="10"/>
+      <c r="A56" s="20" t="s">
+        <v>129</v>
+      </c>
+      <c r="B56" s="21" t="s">
+        <v>130</v>
+      </c>
+      <c r="C56" s="20" t="s">
+        <v>131</v>
+      </c>
+      <c r="D56" s="26" t="s">
+        <v>182</v>
+      </c>
       <c r="E56" s="10"/>
       <c r="F56" s="10"/>
       <c r="G56" s="10"/>
       <c r="H56" s="10"/>
     </row>
-    <row r="57" spans="1:8" ht="15.75" customHeight="1"/>
-    <row r="58" spans="1:8" ht="15.75" customHeight="1"/>
-    <row r="59" spans="1:8" ht="15.75" customHeight="1"/>
-    <row r="60" spans="1:8" ht="15.75" customHeight="1"/>
-    <row r="61" spans="1:8" ht="15.75" customHeight="1"/>
-    <row r="62" spans="1:8" ht="15.75" customHeight="1"/>
-    <row r="63" spans="1:8" ht="15.75" customHeight="1"/>
-    <row r="64" spans="1:8" ht="15.75" customHeight="1"/>
-    <row r="65" ht="15.75" customHeight="1"/>
-    <row r="66" ht="15.75" customHeight="1"/>
-    <row r="67" ht="15.75" customHeight="1"/>
-    <row r="68" ht="15.75" customHeight="1"/>
-    <row r="69" ht="15.75" customHeight="1"/>
-    <row r="70" ht="15.75" customHeight="1"/>
-    <row r="71" ht="15.75" customHeight="1"/>
-    <row r="72" ht="15.75" customHeight="1"/>
-    <row r="73" ht="15.75" customHeight="1"/>
-    <row r="74" ht="15.75" customHeight="1"/>
-    <row r="75" ht="15.75" customHeight="1"/>
-    <row r="76" ht="15.75" customHeight="1"/>
-    <row r="77" ht="15.75" customHeight="1"/>
-    <row r="78" ht="15.75" customHeight="1"/>
-    <row r="79" ht="15.75" customHeight="1"/>
-    <row r="80" ht="15.75" customHeight="1"/>
-    <row r="81" ht="15.75" customHeight="1"/>
-    <row r="82" ht="15.75" customHeight="1"/>
-    <row r="83" ht="15.75" customHeight="1"/>
-    <row r="84" ht="15.75" customHeight="1"/>
-    <row r="85" ht="15.75" customHeight="1"/>
-    <row r="86" ht="15.75" customHeight="1"/>
-    <row r="87" ht="15.75" customHeight="1"/>
-    <row r="88" ht="15.75" customHeight="1"/>
-    <row r="89" ht="15.75" customHeight="1"/>
-    <row r="90" ht="15.75" customHeight="1"/>
-    <row r="91" ht="15.75" customHeight="1"/>
-    <row r="92" ht="15.75" customHeight="1"/>
-    <row r="93" ht="15.75" customHeight="1"/>
-    <row r="94" ht="15.75" customHeight="1"/>
-    <row r="95" ht="15.75" customHeight="1"/>
-    <row r="96" ht="15.75" customHeight="1"/>
-    <row r="97" ht="15.75" customHeight="1"/>
-    <row r="98" ht="15.75" customHeight="1"/>
-    <row r="99" ht="15.75" customHeight="1"/>
-    <row r="100" ht="15.75" customHeight="1"/>
-    <row r="101" ht="15.75" customHeight="1"/>
-    <row r="102" ht="15.75" customHeight="1"/>
-    <row r="103" ht="15.75" customHeight="1"/>
-    <row r="104" ht="15.75" customHeight="1"/>
-    <row r="105" ht="15.75" customHeight="1"/>
-    <row r="106" ht="15.75" customHeight="1"/>
-    <row r="107" ht="15.75" customHeight="1"/>
-    <row r="108" ht="15.75" customHeight="1"/>
-    <row r="109" ht="15.75" customHeight="1"/>
-    <row r="110" ht="15.75" customHeight="1"/>
-    <row r="111" ht="15.75" customHeight="1"/>
-    <row r="112" ht="15.75" customHeight="1"/>
-    <row r="113" ht="15.75" customHeight="1"/>
-    <row r="114" ht="15.75" customHeight="1"/>
-    <row r="115" ht="15.75" customHeight="1"/>
-    <row r="116" ht="15.75" customHeight="1"/>
-    <row r="117" ht="15.75" customHeight="1"/>
-    <row r="118" ht="15.75" customHeight="1"/>
-    <row r="119" ht="15.75" customHeight="1"/>
-    <row r="120" ht="15.75" customHeight="1"/>
-    <row r="121" ht="15.75" customHeight="1"/>
-    <row r="122" ht="15.75" customHeight="1"/>
-    <row r="123" ht="15.75" customHeight="1"/>
-    <row r="124" ht="15.75" customHeight="1"/>
-    <row r="125" ht="15.75" customHeight="1"/>
-    <row r="126" ht="15.75" customHeight="1"/>
-    <row r="127" ht="15.75" customHeight="1"/>
-    <row r="128" ht="15.75" customHeight="1"/>
+    <row r="57" spans="1:8" ht="15.75" customHeight="1">
+      <c r="A57" s="22" t="s">
+        <v>131</v>
+      </c>
+      <c r="B57" s="22" t="s">
+        <v>132</v>
+      </c>
+      <c r="C57" s="22" t="s">
+        <v>133</v>
+      </c>
+      <c r="D57" s="23" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="58" spans="1:8" ht="15.75" customHeight="1">
+      <c r="A58" s="22" t="s">
+        <v>134</v>
+      </c>
+      <c r="B58" s="24" t="s">
+        <v>135</v>
+      </c>
+      <c r="C58" s="22" t="s">
+        <v>141</v>
+      </c>
+      <c r="D58" s="23" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="59" spans="1:8" ht="15.75" customHeight="1">
+      <c r="A59" s="22" t="s">
+        <v>141</v>
+      </c>
+      <c r="B59" s="25" t="s">
+        <v>136</v>
+      </c>
+      <c r="C59" s="22" t="s">
+        <v>145</v>
+      </c>
+      <c r="D59" s="23" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="60" spans="1:8" ht="15.75" customHeight="1">
+      <c r="A60" s="22" t="s">
+        <v>142</v>
+      </c>
+      <c r="B60" s="24" t="s">
+        <v>137</v>
+      </c>
+      <c r="C60" s="22" t="s">
+        <v>143</v>
+      </c>
+      <c r="D60" s="23" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="61" spans="1:8" ht="15.75" customHeight="1">
+      <c r="A61" s="22" t="s">
+        <v>143</v>
+      </c>
+      <c r="B61" s="24" t="s">
+        <v>138</v>
+      </c>
+      <c r="C61" s="22" t="s">
+        <v>144</v>
+      </c>
+      <c r="D61" s="23" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="62" spans="1:8" ht="15.75" customHeight="1">
+      <c r="A62" s="22" t="s">
+        <v>146</v>
+      </c>
+      <c r="B62" s="25" t="s">
+        <v>139</v>
+      </c>
+      <c r="C62" s="22" t="s">
+        <v>163</v>
+      </c>
+      <c r="D62" s="23" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="63" spans="1:8" ht="15.75" customHeight="1">
+      <c r="A63" s="22" t="s">
+        <v>147</v>
+      </c>
+      <c r="B63" s="24" t="s">
+        <v>148</v>
+      </c>
+      <c r="C63" s="22" t="s">
+        <v>156</v>
+      </c>
+      <c r="D63" s="23" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="64" spans="1:8" ht="15.75" customHeight="1">
+      <c r="A64" s="22" t="s">
+        <v>156</v>
+      </c>
+      <c r="B64" s="25" t="s">
+        <v>149</v>
+      </c>
+      <c r="C64" s="22" t="s">
+        <v>162</v>
+      </c>
+      <c r="D64" s="23" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A65" s="22" t="s">
+        <v>157</v>
+      </c>
+      <c r="B65" s="24" t="s">
+        <v>150</v>
+      </c>
+      <c r="C65" s="22" t="s">
+        <v>158</v>
+      </c>
+      <c r="D65" s="23" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="66" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A66" s="22" t="s">
+        <v>158</v>
+      </c>
+      <c r="B66" s="24" t="s">
+        <v>151</v>
+      </c>
+      <c r="C66" s="22" t="s">
+        <v>159</v>
+      </c>
+      <c r="D66" s="23" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="67" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A67" s="22" t="s">
+        <v>159</v>
+      </c>
+      <c r="B67" s="25" t="s">
+        <v>152</v>
+      </c>
+      <c r="C67" s="22" t="s">
+        <v>140</v>
+      </c>
+      <c r="D67" s="23" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="68" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A68" s="22" t="s">
+        <v>140</v>
+      </c>
+      <c r="B68" s="24" t="s">
+        <v>153</v>
+      </c>
+      <c r="C68" s="22" t="s">
+        <v>160</v>
+      </c>
+      <c r="D68" s="23" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="69" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A69" s="22" t="s">
+        <v>160</v>
+      </c>
+      <c r="B69" s="24" t="s">
+        <v>154</v>
+      </c>
+      <c r="C69" s="22" t="s">
+        <v>161</v>
+      </c>
+      <c r="D69" s="23" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="70" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A70" s="22" t="s">
+        <v>164</v>
+      </c>
+      <c r="B70" s="25" t="s">
+        <v>155</v>
+      </c>
+      <c r="C70" s="22" t="s">
+        <v>165</v>
+      </c>
+      <c r="D70" s="23" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="71" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A71" s="23"/>
+      <c r="B71" s="23"/>
+      <c r="C71" s="23"/>
+      <c r="D71" s="23"/>
+    </row>
+    <row r="72" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A72" s="23"/>
+      <c r="B72" s="23"/>
+      <c r="C72" s="23"/>
+      <c r="D72" s="23"/>
+    </row>
+    <row r="73" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A73" s="23"/>
+      <c r="B73" s="23"/>
+      <c r="C73" s="23"/>
+      <c r="D73" s="23"/>
+    </row>
+    <row r="74" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A74" s="23"/>
+      <c r="B74" s="23"/>
+      <c r="C74" s="23"/>
+      <c r="D74" s="23"/>
+    </row>
+    <row r="75" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A75" s="23"/>
+      <c r="B75" s="23"/>
+      <c r="C75" s="23"/>
+      <c r="D75" s="23"/>
+    </row>
+    <row r="76" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A76" s="23"/>
+      <c r="B76" s="23"/>
+      <c r="C76" s="23"/>
+      <c r="D76" s="23"/>
+    </row>
+    <row r="77" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A77" s="23"/>
+      <c r="B77" s="23"/>
+      <c r="C77" s="23"/>
+      <c r="D77" s="23"/>
+    </row>
+    <row r="78" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A78" s="23"/>
+      <c r="B78" s="23"/>
+      <c r="C78" s="23"/>
+      <c r="D78" s="23"/>
+    </row>
+    <row r="79" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A79" s="23"/>
+      <c r="B79" s="23"/>
+      <c r="C79" s="23"/>
+      <c r="D79" s="23"/>
+    </row>
+    <row r="80" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A80" s="23"/>
+      <c r="B80" s="23"/>
+      <c r="C80" s="23"/>
+      <c r="D80" s="23"/>
+    </row>
+    <row r="81" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A81" s="23"/>
+      <c r="B81" s="23"/>
+      <c r="C81" s="23"/>
+      <c r="D81" s="23"/>
+    </row>
+    <row r="82" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A82" s="23"/>
+      <c r="B82" s="23"/>
+      <c r="C82" s="23"/>
+      <c r="D82" s="23"/>
+    </row>
+    <row r="83" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A83" s="23"/>
+      <c r="B83" s="23"/>
+      <c r="C83" s="23"/>
+      <c r="D83" s="23"/>
+    </row>
+    <row r="84" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A84" s="23"/>
+      <c r="B84" s="23"/>
+      <c r="C84" s="23"/>
+      <c r="D84" s="23"/>
+    </row>
+    <row r="85" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A85" s="23"/>
+      <c r="B85" s="23"/>
+      <c r="C85" s="23"/>
+      <c r="D85" s="23"/>
+    </row>
+    <row r="86" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A86" s="23"/>
+      <c r="B86" s="23"/>
+      <c r="C86" s="23"/>
+      <c r="D86" s="23"/>
+    </row>
+    <row r="87" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A87" s="23"/>
+      <c r="B87" s="23"/>
+      <c r="C87" s="23"/>
+      <c r="D87" s="23"/>
+    </row>
+    <row r="88" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A88" s="23"/>
+      <c r="B88" s="23"/>
+      <c r="C88" s="23"/>
+      <c r="D88" s="23"/>
+    </row>
+    <row r="89" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A89" s="23"/>
+      <c r="B89" s="23"/>
+      <c r="C89" s="23"/>
+      <c r="D89" s="23"/>
+    </row>
+    <row r="90" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A90" s="23"/>
+      <c r="B90" s="23"/>
+      <c r="C90" s="23"/>
+      <c r="D90" s="23"/>
+    </row>
+    <row r="91" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A91" s="23"/>
+      <c r="B91" s="23"/>
+      <c r="C91" s="23"/>
+      <c r="D91" s="23"/>
+    </row>
+    <row r="92" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A92" s="23"/>
+      <c r="B92" s="23"/>
+      <c r="C92" s="23"/>
+      <c r="D92" s="23"/>
+    </row>
+    <row r="93" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A93" s="23"/>
+      <c r="B93" s="23"/>
+      <c r="C93" s="23"/>
+      <c r="D93" s="23"/>
+    </row>
+    <row r="94" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A94" s="23"/>
+      <c r="B94" s="23"/>
+      <c r="C94" s="23"/>
+      <c r="D94" s="23"/>
+    </row>
+    <row r="95" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A95" s="23"/>
+      <c r="B95" s="23"/>
+      <c r="C95" s="23"/>
+      <c r="D95" s="23"/>
+    </row>
+    <row r="96" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A96" s="23"/>
+      <c r="B96" s="23"/>
+      <c r="C96" s="23"/>
+      <c r="D96" s="23"/>
+    </row>
+    <row r="97" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A97" s="23"/>
+      <c r="B97" s="23"/>
+      <c r="C97" s="23"/>
+      <c r="D97" s="23"/>
+    </row>
+    <row r="98" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A98" s="23"/>
+      <c r="B98" s="23"/>
+      <c r="C98" s="23"/>
+      <c r="D98" s="23"/>
+    </row>
+    <row r="99" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A99" s="23"/>
+      <c r="B99" s="23"/>
+      <c r="C99" s="23"/>
+      <c r="D99" s="23"/>
+    </row>
+    <row r="100" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A100" s="23"/>
+      <c r="B100" s="23"/>
+      <c r="C100" s="23"/>
+      <c r="D100" s="23"/>
+    </row>
+    <row r="101" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A101" s="23"/>
+      <c r="B101" s="23"/>
+      <c r="C101" s="23"/>
+      <c r="D101" s="23"/>
+    </row>
+    <row r="102" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A102" s="23"/>
+      <c r="B102" s="23"/>
+      <c r="C102" s="23"/>
+      <c r="D102" s="23"/>
+    </row>
+    <row r="103" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A103" s="23"/>
+      <c r="B103" s="23"/>
+      <c r="C103" s="23"/>
+      <c r="D103" s="23"/>
+    </row>
+    <row r="104" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A104" s="23"/>
+      <c r="B104" s="23"/>
+      <c r="C104" s="23"/>
+    </row>
+    <row r="105" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A105" s="23"/>
+      <c r="B105" s="23"/>
+      <c r="C105" s="23"/>
+    </row>
+    <row r="106" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A106" s="23"/>
+      <c r="B106" s="23"/>
+      <c r="C106" s="23"/>
+    </row>
+    <row r="107" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A107" s="23"/>
+      <c r="B107" s="23"/>
+      <c r="C107" s="23"/>
+    </row>
+    <row r="108" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A108" s="23"/>
+      <c r="B108" s="23"/>
+      <c r="C108" s="23"/>
+    </row>
+    <row r="109" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A109" s="23"/>
+      <c r="B109" s="23"/>
+      <c r="C109" s="23"/>
+    </row>
+    <row r="110" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A110" s="23"/>
+      <c r="B110" s="23"/>
+      <c r="C110" s="23"/>
+    </row>
+    <row r="111" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A111" s="23"/>
+      <c r="B111" s="23"/>
+      <c r="C111" s="23"/>
+    </row>
+    <row r="112" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A112" s="23"/>
+      <c r="B112" s="23"/>
+      <c r="C112" s="23"/>
+    </row>
+    <row r="113" spans="1:3" ht="15.75" customHeight="1">
+      <c r="A113" s="23"/>
+      <c r="B113" s="23"/>
+      <c r="C113" s="23"/>
+    </row>
+    <row r="114" spans="1:3" ht="15.75" customHeight="1">
+      <c r="A114" s="23"/>
+      <c r="B114" s="23"/>
+      <c r="C114" s="23"/>
+    </row>
+    <row r="115" spans="1:3" ht="15.75" customHeight="1">
+      <c r="A115" s="23"/>
+      <c r="B115" s="23"/>
+      <c r="C115" s="23"/>
+    </row>
+    <row r="116" spans="1:3" ht="15.75" customHeight="1">
+      <c r="A116" s="23"/>
+      <c r="B116" s="23"/>
+      <c r="C116" s="23"/>
+    </row>
+    <row r="117" spans="1:3" ht="15.75" customHeight="1">
+      <c r="A117" s="23"/>
+      <c r="B117" s="23"/>
+      <c r="C117" s="23"/>
+    </row>
+    <row r="118" spans="1:3" ht="15.75" customHeight="1">
+      <c r="A118" s="23"/>
+      <c r="B118" s="23"/>
+      <c r="C118" s="23"/>
+    </row>
+    <row r="119" spans="1:3" ht="15.75" customHeight="1">
+      <c r="A119" s="23"/>
+      <c r="B119" s="23"/>
+      <c r="C119" s="23"/>
+    </row>
+    <row r="120" spans="1:3" ht="15.75" customHeight="1">
+      <c r="A120" s="23"/>
+      <c r="B120" s="23"/>
+      <c r="C120" s="23"/>
+    </row>
+    <row r="121" spans="1:3" ht="15.75" customHeight="1">
+      <c r="A121" s="23"/>
+      <c r="B121" s="23"/>
+      <c r="C121" s="23"/>
+    </row>
+    <row r="122" spans="1:3" ht="15.75" customHeight="1">
+      <c r="A122" s="23"/>
+      <c r="B122" s="23"/>
+      <c r="C122" s="23"/>
+    </row>
+    <row r="123" spans="1:3" ht="15.75" customHeight="1"/>
+    <row r="124" spans="1:3" ht="15.75" customHeight="1"/>
+    <row r="125" spans="1:3" ht="15.75" customHeight="1"/>
+    <row r="126" spans="1:3" ht="15.75" customHeight="1"/>
+    <row r="127" spans="1:3" ht="15.75" customHeight="1"/>
+    <row r="128" spans="1:3" ht="15.75" customHeight="1"/>
     <row r="129" ht="15.75" customHeight="1"/>
     <row r="130" ht="15.75" customHeight="1"/>
     <row r="131" ht="15.75" customHeight="1"/>

--- a/JsonConverter/ExcelFiles/0_MindDialogue.xlsx
+++ b/JsonConverter/ExcelFiles/0_MindDialogue.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\0_SonghaUnityGame\JsonConverter\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A8403DAC-1E6F-4971-8D2F-531DEE02B6D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A51B2A2-6C5A-4818-9E58-7AEA2760D40D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="360" yWindow="960" windowWidth="28185" windowHeight="14490" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2333,9 +2333,6 @@
     <t>Sprite/Out Class cry</t>
   </si>
   <si>
-    <t>Sprite/Class Room study.</t>
-  </si>
-  <si>
     <t>Sprite/CU work</t>
   </si>
   <si>
@@ -2357,6 +2354,10 @@
   </si>
   <si>
     <t>Sprite/Out Class cry</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Sprite/Class Room study</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -3804,7 +3805,7 @@
         <v>102</v>
       </c>
       <c r="D43" s="11" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="E43" s="8"/>
       <c r="F43" s="8"/>
@@ -3822,7 +3823,7 @@
         <v>104</v>
       </c>
       <c r="D44" s="11" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="E44" s="8"/>
       <c r="F44" s="8"/>
@@ -3840,7 +3841,7 @@
         <v>108</v>
       </c>
       <c r="D45" s="11" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="E45" s="8"/>
       <c r="F45" s="8"/>
@@ -3875,8 +3876,8 @@
       <c r="C47" s="15" t="s">
         <v>113</v>
       </c>
-      <c r="D47" s="9" t="s">
-        <v>178</v>
+      <c r="D47" s="15" t="s">
+        <v>185</v>
       </c>
       <c r="E47" s="9"/>
       <c r="F47" s="9"/>
@@ -3893,8 +3894,8 @@
       <c r="C48" s="15" t="s">
         <v>115</v>
       </c>
-      <c r="D48" s="9" t="s">
-        <v>178</v>
+      <c r="D48" s="15" t="s">
+        <v>185</v>
       </c>
       <c r="E48" s="9"/>
       <c r="F48" s="9"/>
@@ -3912,7 +3913,7 @@
         <v>117</v>
       </c>
       <c r="D49" s="9" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="E49" s="9"/>
       <c r="F49" s="9"/>
@@ -3930,7 +3931,7 @@
         <v>119</v>
       </c>
       <c r="D50" s="9" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="E50" s="9"/>
       <c r="F50" s="9"/>
@@ -3948,7 +3949,7 @@
         <v>121</v>
       </c>
       <c r="D51" s="9" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="E51" s="9"/>
       <c r="F51" s="9"/>
@@ -3966,7 +3967,7 @@
         <v>123</v>
       </c>
       <c r="D52" s="9" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="E52" s="9"/>
       <c r="F52" s="9"/>
@@ -3984,7 +3985,7 @@
         <v>124</v>
       </c>
       <c r="D53" s="17" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="E53" s="10"/>
       <c r="F53" s="10"/>
@@ -4002,7 +4003,7 @@
         <v>127</v>
       </c>
       <c r="D54" s="10" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="E54" s="10"/>
       <c r="F54" s="10"/>
@@ -4020,7 +4021,7 @@
         <v>129</v>
       </c>
       <c r="D55" s="10" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="E55" s="10"/>
       <c r="F55" s="10"/>
@@ -4038,7 +4039,7 @@
         <v>131</v>
       </c>
       <c r="D56" s="26" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="E56" s="10"/>
       <c r="F56" s="10"/>
@@ -4056,7 +4057,7 @@
         <v>133</v>
       </c>
       <c r="D57" s="23" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="58" spans="1:8" ht="15.75" customHeight="1">
@@ -4070,7 +4071,7 @@
         <v>141</v>
       </c>
       <c r="D58" s="23" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="59" spans="1:8" ht="15.75" customHeight="1">
@@ -4084,7 +4085,7 @@
         <v>145</v>
       </c>
       <c r="D59" s="23" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="60" spans="1:8" ht="15.75" customHeight="1">
@@ -4098,7 +4099,7 @@
         <v>143</v>
       </c>
       <c r="D60" s="23" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="61" spans="1:8" ht="15.75" customHeight="1">
@@ -4112,7 +4113,7 @@
         <v>144</v>
       </c>
       <c r="D61" s="23" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="62" spans="1:8" ht="15.75" customHeight="1">
@@ -4126,7 +4127,7 @@
         <v>163</v>
       </c>
       <c r="D62" s="23" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="63" spans="1:8" ht="15.75" customHeight="1">
@@ -4140,7 +4141,7 @@
         <v>156</v>
       </c>
       <c r="D63" s="23" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="64" spans="1:8" ht="15.75" customHeight="1">
@@ -4154,7 +4155,7 @@
         <v>162</v>
       </c>
       <c r="D64" s="23" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="65" spans="1:4" ht="15.75" customHeight="1">
@@ -4168,7 +4169,7 @@
         <v>158</v>
       </c>
       <c r="D65" s="23" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="66" spans="1:4" ht="15.75" customHeight="1">
@@ -4182,7 +4183,7 @@
         <v>159</v>
       </c>
       <c r="D66" s="23" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="67" spans="1:4" ht="15.75" customHeight="1">
@@ -4196,7 +4197,7 @@
         <v>140</v>
       </c>
       <c r="D67" s="23" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="68" spans="1:4" ht="15.75" customHeight="1">
@@ -4210,7 +4211,7 @@
         <v>160</v>
       </c>
       <c r="D68" s="23" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="69" spans="1:4" ht="15.75" customHeight="1">
@@ -4224,7 +4225,7 @@
         <v>161</v>
       </c>
       <c r="D69" s="23" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="70" spans="1:4" ht="15.75" customHeight="1">
@@ -4238,7 +4239,7 @@
         <v>165</v>
       </c>
       <c r="D70" s="23" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="71" spans="1:4" ht="15.75" customHeight="1">

--- a/JsonConverter/ExcelFiles/0_MindDialogue.xlsx
+++ b/JsonConverter/ExcelFiles/0_MindDialogue.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A51B2A2-6C5A-4818-9E58-7AEA2760D40D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="360" yWindow="960" windowWidth="28185" windowHeight="14490" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="615" yWindow="990" windowWidth="28185" windowHeight="14490" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Table_MindDialogue" sheetId="1" r:id="rId1"/>

--- a/JsonConverter/ExcelFiles/0_MindDialogue.xlsx
+++ b/JsonConverter/ExcelFiles/0_MindDialogue.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\0_SonghaUnityGame\JsonConverter\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A51B2A2-6C5A-4818-9E58-7AEA2760D40D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66349474-917D-4999-A6D4-DA6B7B904050}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="615" yWindow="990" windowWidth="28185" windowHeight="14490" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="435" yWindow="930" windowWidth="28185" windowHeight="14490" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Table_MindDialogue" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="286" uniqueCount="186">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="313" uniqueCount="206">
   <si>
     <t>CharacterDataId</t>
   </si>
@@ -2320,44 +2320,122 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
+    <t>Sprite/Before Sleep</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Sprite/morning empty Room</t>
+  </si>
+  <si>
+    <t>Sprite/Out Class cry</t>
+  </si>
+  <si>
+    <t>Sprite/CU work</t>
+  </si>
+  <si>
+    <t>Sprite/CU cry</t>
+  </si>
+  <si>
+    <t>Sprite/CU work</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Sprite/Cu go home</t>
+  </si>
+  <si>
+    <t>Sprite/CU go home cry</t>
+  </si>
+  <si>
+    <t>Sprite/Class Room</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Sprite/Out Class cry</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Sprite/Class Room study</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Sprite/Out Class</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>mindDialogue_Opening_1_1_279</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>이제껏 나는 그녀의 전화를 단 한번도 먼저 끊은적 없었다.</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">mindDialogue_Opening_1_1_280 </t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>그러나 이번 만큼은 아픈 마음을 견딜 수 없어서 먼저 끊었다.</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>mindDialogue_Opening_1_1_281</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>집으로 가야하는데 한참을 차 안에서 눈물 흘렸다.</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>mindDialogue_Opening_1_1_280</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Sprite/CU go home cry</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>mindDialogue_Opening_1_1_282</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>그렇지만 나름 찝찝했던거만큼은 조금이나마 해결되는 밤이었다.</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>mindDialogue_Opening_1_1_283</t>
+  </si>
+  <si>
+    <t>mindDialogue_Opening_1_1_283</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>그렇게 집으로 돌아와 힘든 시간을 보냈다.</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>mindDialogue_Opening_1_1_284</t>
+  </si>
+  <si>
+    <t>mindDialogue_Opening_1_1_284</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>깊이 생각하지 않으려 했지만, 자꾸만 가슴 한 켠이 짓눌리듯 아파왔다.</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>mindDialogue_Opening_1_1_285</t>
+  </si>
+  <si>
+    <t>mindDialogue_Opening_1_1_285</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>그렇게…잠 못들고 공허한 밤을 보냈다.</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
     <t>Sprite/Dark empty Room</t>
-  </si>
-  <si>
-    <t>Sprite/Before Sleep</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Sprite/morning empty Room</t>
-  </si>
-  <si>
-    <t>Sprite/Out Class cry</t>
-  </si>
-  <si>
-    <t>Sprite/CU work</t>
-  </si>
-  <si>
-    <t>Sprite/CU cry</t>
-  </si>
-  <si>
-    <t>Sprite/CU work</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Sprite/Cu go home</t>
-  </si>
-  <si>
-    <t>Sprite/CU go home cry</t>
-  </si>
-  <si>
-    <t>Sprite/Class Room</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Sprite/Out Class cry</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Sprite/Class Room study</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -2520,7 +2598,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -2601,6 +2679,9 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -3102,7 +3183,7 @@
         <v>15</v>
       </c>
       <c r="D4" s="27" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="F4" s="1" t="s">
         <v>10</v>
@@ -3121,7 +3202,7 @@
         <v>21</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="E5" s="1"/>
       <c r="F5" s="1"/>
@@ -3679,7 +3760,7 @@
         <v>87</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="E36" s="3"/>
       <c r="F36" s="3"/>
@@ -3696,8 +3777,8 @@
       <c r="C37" s="11" t="s">
         <v>89</v>
       </c>
-      <c r="D37" s="8" t="s">
-        <v>174</v>
+      <c r="D37" s="11" t="s">
+        <v>205</v>
       </c>
       <c r="E37" s="8"/>
       <c r="F37" s="8"/>
@@ -3714,8 +3795,8 @@
       <c r="C38" s="11" t="s">
         <v>92</v>
       </c>
-      <c r="D38" s="8" t="s">
-        <v>174</v>
+      <c r="D38" s="11" t="s">
+        <v>205</v>
       </c>
       <c r="E38" s="8"/>
       <c r="F38" s="8"/>
@@ -3733,7 +3814,7 @@
         <v>94</v>
       </c>
       <c r="D39" s="8" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="E39" s="8"/>
       <c r="F39" s="8"/>
@@ -3751,7 +3832,7 @@
         <v>97</v>
       </c>
       <c r="D40" s="8" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="E40" s="8"/>
       <c r="F40" s="8"/>
@@ -3769,7 +3850,7 @@
         <v>98</v>
       </c>
       <c r="D41" s="8" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="E41" s="8"/>
       <c r="F41" s="8"/>
@@ -3787,7 +3868,7 @@
         <v>99</v>
       </c>
       <c r="D42" s="8" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="E42" s="8"/>
       <c r="F42" s="8"/>
@@ -3805,7 +3886,7 @@
         <v>102</v>
       </c>
       <c r="D43" s="11" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E43" s="8"/>
       <c r="F43" s="8"/>
@@ -3823,7 +3904,7 @@
         <v>104</v>
       </c>
       <c r="D44" s="11" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="E44" s="8"/>
       <c r="F44" s="8"/>
@@ -3841,7 +3922,7 @@
         <v>108</v>
       </c>
       <c r="D45" s="11" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="E45" s="8"/>
       <c r="F45" s="8"/>
@@ -3859,7 +3940,7 @@
         <v>110</v>
       </c>
       <c r="D46" s="8" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="E46" s="8"/>
       <c r="F46" s="8"/>
@@ -3877,7 +3958,7 @@
         <v>113</v>
       </c>
       <c r="D47" s="15" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="E47" s="9"/>
       <c r="F47" s="9"/>
@@ -3895,7 +3976,7 @@
         <v>115</v>
       </c>
       <c r="D48" s="15" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="E48" s="9"/>
       <c r="F48" s="9"/>
@@ -3913,7 +3994,7 @@
         <v>117</v>
       </c>
       <c r="D49" s="9" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="E49" s="9"/>
       <c r="F49" s="9"/>
@@ -3931,7 +4012,7 @@
         <v>119</v>
       </c>
       <c r="D50" s="9" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="E50" s="9"/>
       <c r="F50" s="9"/>
@@ -3949,7 +4030,7 @@
         <v>121</v>
       </c>
       <c r="D51" s="9" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="E51" s="9"/>
       <c r="F51" s="9"/>
@@ -3967,7 +4048,7 @@
         <v>123</v>
       </c>
       <c r="D52" s="9" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="E52" s="9"/>
       <c r="F52" s="9"/>
@@ -3985,7 +4066,7 @@
         <v>124</v>
       </c>
       <c r="D53" s="17" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="E53" s="10"/>
       <c r="F53" s="10"/>
@@ -4003,7 +4084,7 @@
         <v>127</v>
       </c>
       <c r="D54" s="10" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="E54" s="10"/>
       <c r="F54" s="10"/>
@@ -4021,7 +4102,7 @@
         <v>129</v>
       </c>
       <c r="D55" s="10" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="E55" s="10"/>
       <c r="F55" s="10"/>
@@ -4039,7 +4120,7 @@
         <v>131</v>
       </c>
       <c r="D56" s="26" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="E56" s="10"/>
       <c r="F56" s="10"/>
@@ -4057,7 +4138,7 @@
         <v>133</v>
       </c>
       <c r="D57" s="23" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="58" spans="1:8" ht="15.75" customHeight="1">
@@ -4071,7 +4152,7 @@
         <v>141</v>
       </c>
       <c r="D58" s="23" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="59" spans="1:8" ht="15.75" customHeight="1">
@@ -4085,7 +4166,7 @@
         <v>145</v>
       </c>
       <c r="D59" s="23" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="60" spans="1:8" ht="15.75" customHeight="1">
@@ -4099,7 +4180,7 @@
         <v>143</v>
       </c>
       <c r="D60" s="23" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="61" spans="1:8" ht="15.75" customHeight="1">
@@ -4113,7 +4194,7 @@
         <v>144</v>
       </c>
       <c r="D61" s="23" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="62" spans="1:8" ht="15.75" customHeight="1">
@@ -4127,7 +4208,7 @@
         <v>163</v>
       </c>
       <c r="D62" s="23" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="63" spans="1:8" ht="15.75" customHeight="1">
@@ -4141,7 +4222,7 @@
         <v>156</v>
       </c>
       <c r="D63" s="23" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="64" spans="1:8" ht="15.75" customHeight="1">
@@ -4155,7 +4236,7 @@
         <v>162</v>
       </c>
       <c r="D64" s="23" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="65" spans="1:4" ht="15.75" customHeight="1">
@@ -4169,7 +4250,7 @@
         <v>158</v>
       </c>
       <c r="D65" s="23" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="66" spans="1:4" ht="15.75" customHeight="1">
@@ -4183,7 +4264,7 @@
         <v>159</v>
       </c>
       <c r="D66" s="23" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="67" spans="1:4" ht="15.75" customHeight="1">
@@ -4197,7 +4278,7 @@
         <v>140</v>
       </c>
       <c r="D67" s="23" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="68" spans="1:4" ht="15.75" customHeight="1">
@@ -4211,7 +4292,7 @@
         <v>160</v>
       </c>
       <c r="D68" s="23" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="69" spans="1:4" ht="15.75" customHeight="1">
@@ -4225,7 +4306,7 @@
         <v>161</v>
       </c>
       <c r="D69" s="23" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="70" spans="1:4" ht="15.75" customHeight="1">
@@ -4238,51 +4319,105 @@
       <c r="C70" s="22" t="s">
         <v>165</v>
       </c>
-      <c r="D70" s="23" t="s">
-        <v>182</v>
+      <c r="D70" s="22" t="s">
+        <v>193</v>
       </c>
     </row>
     <row r="71" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A71" s="23"/>
-      <c r="B71" s="23"/>
-      <c r="C71" s="23"/>
-      <c r="D71" s="23"/>
+      <c r="A71" s="22" t="s">
+        <v>186</v>
+      </c>
+      <c r="B71" s="28" t="s">
+        <v>187</v>
+      </c>
+      <c r="C71" s="22" t="s">
+        <v>192</v>
+      </c>
+      <c r="D71" s="22" t="s">
+        <v>193</v>
+      </c>
     </row>
     <row r="72" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A72" s="23"/>
-      <c r="B72" s="23"/>
-      <c r="C72" s="23"/>
-      <c r="D72" s="23"/>
+      <c r="A72" s="22" t="s">
+        <v>188</v>
+      </c>
+      <c r="B72" s="28" t="s">
+        <v>189</v>
+      </c>
+      <c r="C72" s="22" t="s">
+        <v>190</v>
+      </c>
+      <c r="D72" s="22" t="s">
+        <v>193</v>
+      </c>
     </row>
     <row r="73" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A73" s="23"/>
-      <c r="B73" s="23"/>
-      <c r="C73" s="23"/>
-      <c r="D73" s="23"/>
+      <c r="A73" s="22" t="s">
+        <v>190</v>
+      </c>
+      <c r="B73" s="28" t="s">
+        <v>191</v>
+      </c>
+      <c r="C73" s="22" t="s">
+        <v>194</v>
+      </c>
+      <c r="D73" s="22" t="s">
+        <v>193</v>
+      </c>
     </row>
     <row r="74" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A74" s="23"/>
-      <c r="B74" s="23"/>
-      <c r="C74" s="23"/>
-      <c r="D74" s="23"/>
+      <c r="A74" s="22" t="s">
+        <v>194</v>
+      </c>
+      <c r="B74" s="28" t="s">
+        <v>195</v>
+      </c>
+      <c r="C74" s="22" t="s">
+        <v>196</v>
+      </c>
+      <c r="D74" s="22" t="s">
+        <v>193</v>
+      </c>
     </row>
     <row r="75" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A75" s="23"/>
-      <c r="B75" s="23"/>
-      <c r="C75" s="23"/>
-      <c r="D75" s="23"/>
+      <c r="A75" s="22" t="s">
+        <v>197</v>
+      </c>
+      <c r="B75" s="28" t="s">
+        <v>198</v>
+      </c>
+      <c r="C75" s="22" t="s">
+        <v>199</v>
+      </c>
+      <c r="D75" s="22" t="s">
+        <v>173</v>
+      </c>
     </row>
     <row r="76" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A76" s="23"/>
-      <c r="B76" s="23"/>
-      <c r="C76" s="23"/>
-      <c r="D76" s="23"/>
+      <c r="A76" s="22" t="s">
+        <v>200</v>
+      </c>
+      <c r="B76" s="28" t="s">
+        <v>201</v>
+      </c>
+      <c r="C76" s="22" t="s">
+        <v>202</v>
+      </c>
+      <c r="D76" s="22" t="s">
+        <v>173</v>
+      </c>
     </row>
     <row r="77" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A77" s="23"/>
-      <c r="B77" s="23"/>
+      <c r="A77" s="22" t="s">
+        <v>203</v>
+      </c>
+      <c r="B77" s="28" t="s">
+        <v>204</v>
+      </c>
       <c r="C77" s="23"/>
-      <c r="D77" s="23"/>
+      <c r="D77" s="22" t="s">
+        <v>205</v>
+      </c>
     </row>
     <row r="78" spans="1:4" ht="15.75" customHeight="1">
       <c r="A78" s="23"/>

--- a/JsonConverter/ExcelFiles/0_MindDialogue.xlsx
+++ b/JsonConverter/ExcelFiles/0_MindDialogue.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\0_SonghaUnityGame\JsonConverter\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66349474-917D-4999-A6D4-DA6B7B904050}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67786F6D-50B4-4BC4-A16F-43CADB29C932}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="435" yWindow="930" windowWidth="28185" windowHeight="14490" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28365" yWindow="945" windowWidth="28185" windowHeight="14490" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Table_MindDialogue" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="313" uniqueCount="206">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="333" uniqueCount="218">
   <si>
     <t>CharacterDataId</t>
   </si>
@@ -2386,10 +2386,6 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>mindDialogue_Opening_1_1_280</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>Sprite/CU go home cry</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -2436,6 +2432,58 @@
   </si>
   <si>
     <t>Sprite/Dark empty Room</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>dateDialogue_Opening_1_1_286</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>mindDialogue_Opening_1_1_287</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>너무나 아프고 외로운 밤이지만, 나는 오히려 결의를 다지는 시간이 되었다.</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>mindDialogue_Opening_1_1_288</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>mindDialogue_Opening_1_1_289</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>누가 보기에도 떳떳한 나를 만들어 그녀 앞에 다시 설 것이다.</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>힘들고 아파도, 멈춰있을 때가 아니라는것을 알고 있다.</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>mindDialogue_Opening_1_1_290</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>이 악물고 버텨 끝내 성장하는 나를 보여 줄 시간이다.</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Sprite/moring CheerUp</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>mindDialogue_Opening_1_1_291</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>하루 하루 최선을 다해서, 포기하지 말고 나를 가꾸는 시간이 되자.</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Sprite/morning empty Room 7-30</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -3778,7 +3826,7 @@
         <v>89</v>
       </c>
       <c r="D37" s="11" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="E37" s="8"/>
       <c r="F37" s="8"/>
@@ -3796,7 +3844,7 @@
         <v>92</v>
       </c>
       <c r="D38" s="11" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="E38" s="8"/>
       <c r="F38" s="8"/>
@@ -4320,7 +4368,7 @@
         <v>165</v>
       </c>
       <c r="D70" s="22" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="71" spans="1:4" ht="15.75" customHeight="1">
@@ -4331,10 +4379,10 @@
         <v>187</v>
       </c>
       <c r="C71" s="22" t="s">
+        <v>188</v>
+      </c>
+      <c r="D71" s="22" t="s">
         <v>192</v>
-      </c>
-      <c r="D71" s="22" t="s">
-        <v>193</v>
       </c>
     </row>
     <row r="72" spans="1:4" ht="15.75" customHeight="1">
@@ -4348,7 +4396,7 @@
         <v>190</v>
       </c>
       <c r="D72" s="22" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="73" spans="1:4" ht="15.75" customHeight="1">
@@ -4359,35 +4407,35 @@
         <v>191</v>
       </c>
       <c r="C73" s="22" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="D73" s="22" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="74" spans="1:4" ht="15.75" customHeight="1">
       <c r="A74" s="22" t="s">
+        <v>193</v>
+      </c>
+      <c r="B74" s="28" t="s">
         <v>194</v>
       </c>
-      <c r="B74" s="28" t="s">
+      <c r="C74" s="22" t="s">
         <v>195</v>
       </c>
-      <c r="C74" s="22" t="s">
-        <v>196</v>
-      </c>
       <c r="D74" s="22" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="75" spans="1:4" ht="15.75" customHeight="1">
       <c r="A75" s="22" t="s">
+        <v>196</v>
+      </c>
+      <c r="B75" s="28" t="s">
         <v>197</v>
       </c>
-      <c r="B75" s="28" t="s">
+      <c r="C75" s="22" t="s">
         <v>198</v>
-      </c>
-      <c r="C75" s="22" t="s">
-        <v>199</v>
       </c>
       <c r="D75" s="22" t="s">
         <v>173</v>
@@ -4395,13 +4443,13 @@
     </row>
     <row r="76" spans="1:4" ht="15.75" customHeight="1">
       <c r="A76" s="22" t="s">
+        <v>199</v>
+      </c>
+      <c r="B76" s="28" t="s">
         <v>200</v>
       </c>
-      <c r="B76" s="28" t="s">
+      <c r="C76" s="22" t="s">
         <v>201</v>
-      </c>
-      <c r="C76" s="22" t="s">
-        <v>202</v>
       </c>
       <c r="D76" s="22" t="s">
         <v>173</v>
@@ -4409,45 +4457,85 @@
     </row>
     <row r="77" spans="1:4" ht="15.75" customHeight="1">
       <c r="A77" s="22" t="s">
+        <v>202</v>
+      </c>
+      <c r="B77" s="28" t="s">
         <v>203</v>
       </c>
-      <c r="B77" s="28" t="s">
+      <c r="C77" s="22" t="s">
+        <v>205</v>
+      </c>
+      <c r="D77" s="22" t="s">
         <v>204</v>
       </c>
-      <c r="C77" s="23"/>
-      <c r="D77" s="22" t="s">
-        <v>205</v>
-      </c>
     </row>
     <row r="78" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A78" s="23"/>
-      <c r="B78" s="23"/>
-      <c r="C78" s="23"/>
-      <c r="D78" s="23"/>
+      <c r="A78" s="22" t="s">
+        <v>206</v>
+      </c>
+      <c r="B78" s="28" t="s">
+        <v>207</v>
+      </c>
+      <c r="C78" s="22" t="s">
+        <v>208</v>
+      </c>
+      <c r="D78" s="22" t="s">
+        <v>217</v>
+      </c>
     </row>
     <row r="79" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A79" s="23"/>
-      <c r="B79" s="23"/>
-      <c r="C79" s="23"/>
-      <c r="D79" s="23"/>
+      <c r="A79" s="22" t="s">
+        <v>208</v>
+      </c>
+      <c r="B79" s="28" t="s">
+        <v>210</v>
+      </c>
+      <c r="C79" s="22" t="s">
+        <v>209</v>
+      </c>
+      <c r="D79" s="22" t="s">
+        <v>217</v>
+      </c>
     </row>
     <row r="80" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A80" s="23"/>
-      <c r="B80" s="23"/>
-      <c r="C80" s="23"/>
-      <c r="D80" s="23"/>
+      <c r="A80" s="22" t="s">
+        <v>209</v>
+      </c>
+      <c r="B80" s="28" t="s">
+        <v>211</v>
+      </c>
+      <c r="C80" s="22" t="s">
+        <v>212</v>
+      </c>
+      <c r="D80" s="22" t="s">
+        <v>217</v>
+      </c>
     </row>
     <row r="81" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A81" s="23"/>
-      <c r="B81" s="23"/>
-      <c r="C81" s="23"/>
-      <c r="D81" s="23"/>
+      <c r="A81" s="22" t="s">
+        <v>212</v>
+      </c>
+      <c r="B81" s="28" t="s">
+        <v>213</v>
+      </c>
+      <c r="C81" s="22" t="s">
+        <v>215</v>
+      </c>
+      <c r="D81" s="22" t="s">
+        <v>214</v>
+      </c>
     </row>
     <row r="82" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A82" s="23"/>
-      <c r="B82" s="23"/>
+      <c r="A82" s="22" t="s">
+        <v>215</v>
+      </c>
+      <c r="B82" s="28" t="s">
+        <v>216</v>
+      </c>
       <c r="C82" s="23"/>
-      <c r="D82" s="23"/>
+      <c r="D82" s="22" t="s">
+        <v>214</v>
+      </c>
     </row>
     <row r="83" spans="1:4" ht="15.75" customHeight="1">
       <c r="A83" s="23"/>

--- a/JsonConverter/ExcelFiles/0_MindDialogue.xlsx
+++ b/JsonConverter/ExcelFiles/0_MindDialogue.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\0_SonghaUnityGame\JsonConverter\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67786F6D-50B4-4BC4-A16F-43CADB29C932}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2902236-5650-4352-8E20-D1FDAD847967}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28365" yWindow="945" windowWidth="28185" windowHeight="14490" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="615" yWindow="780" windowWidth="28185" windowHeight="14490" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Table_MindDialogue" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="333" uniqueCount="218">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="356" uniqueCount="234">
   <si>
     <t>CharacterDataId</t>
   </si>
@@ -2484,6 +2484,80 @@
   </si>
   <si>
     <t>Sprite/morning empty Room 7-30</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>mindDialogue_Opening_1_1_292</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>문이 벌컥 열리며)</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>normalDialogue_Opening_1_1_293</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>mindDialogue_Opening_1_1_303</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>완성된 나를 위해서는 사소한 거라도 성실히 해야한다.</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>이제 서둘러 나갈 준비를 해야겠다.</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>mindDialogue_Opening_1_1_304</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Sprite/morning Emptyroom</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>mindDialogue_Opening_1_1_305</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>mindDialogue_Opening_1_1_307</t>
+  </si>
+  <si>
+    <t>준비를 마치고 문 앞에 서 있다.</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>이제 이 문을 나가는 순간부터 나는 완성된 나로 다시 태어난다.</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Sprite/Door</t>
+  </si>
+  <si>
+    <t>mindDialogue_Opening_1_1_306</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Sprite/Door</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>mindDialogue_Opening_1_1_307</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -4519,7 +4593,7 @@
         <v>213</v>
       </c>
       <c r="C81" s="22" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="D81" s="22" t="s">
         <v>214</v>
@@ -4532,49 +4606,95 @@
       <c r="B82" s="28" t="s">
         <v>216</v>
       </c>
-      <c r="C82" s="23"/>
+      <c r="C82" s="22" t="s">
+        <v>218</v>
+      </c>
       <c r="D82" s="22" t="s">
         <v>214</v>
       </c>
     </row>
     <row r="83" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A83" s="23"/>
-      <c r="B83" s="23"/>
-      <c r="C83" s="23"/>
-      <c r="D83" s="23"/>
+      <c r="A83" s="22" t="s">
+        <v>218</v>
+      </c>
+      <c r="B83" s="22" t="s">
+        <v>219</v>
+      </c>
+      <c r="C83" s="22" t="s">
+        <v>220</v>
+      </c>
+      <c r="D83" s="22" t="s">
+        <v>214</v>
+      </c>
     </row>
     <row r="84" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A84" s="23"/>
-      <c r="B84" s="23"/>
-      <c r="C84" s="23"/>
-      <c r="D84" s="23"/>
+      <c r="A84" s="22" t="s">
+        <v>221</v>
+      </c>
+      <c r="B84" s="28" t="s">
+        <v>222</v>
+      </c>
+      <c r="C84" s="22" t="s">
+        <v>224</v>
+      </c>
+      <c r="D84" s="22" t="s">
+        <v>225</v>
+      </c>
     </row>
     <row r="85" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A85" s="23"/>
-      <c r="B85" s="23"/>
-      <c r="C85" s="23"/>
-      <c r="D85" s="23"/>
+      <c r="A85" s="22" t="s">
+        <v>224</v>
+      </c>
+      <c r="B85" s="28" t="s">
+        <v>223</v>
+      </c>
+      <c r="C85" s="22" t="s">
+        <v>226</v>
+      </c>
+      <c r="D85" s="22" t="s">
+        <v>225</v>
+      </c>
     </row>
     <row r="86" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A86" s="23"/>
-      <c r="B86" s="23"/>
-      <c r="C86" s="23"/>
-      <c r="D86" s="23"/>
+      <c r="A86" s="22" t="s">
+        <v>226</v>
+      </c>
+      <c r="B86" s="28" t="s">
+        <v>228</v>
+      </c>
+      <c r="C86" s="22" t="s">
+        <v>231</v>
+      </c>
+      <c r="D86" s="23" t="s">
+        <v>230</v>
+      </c>
     </row>
     <row r="87" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A87" s="23"/>
-      <c r="B87" s="23"/>
-      <c r="C87" s="23"/>
-      <c r="D87" s="23"/>
+      <c r="A87" s="22" t="s">
+        <v>231</v>
+      </c>
+      <c r="B87" s="28" t="s">
+        <v>229</v>
+      </c>
+      <c r="C87" s="22" t="s">
+        <v>227</v>
+      </c>
+      <c r="D87" s="22" t="s">
+        <v>232</v>
+      </c>
     </row>
     <row r="88" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A88" s="23"/>
+      <c r="A88" s="22" t="s">
+        <v>233</v>
+      </c>
       <c r="B88" s="23"/>
       <c r="C88" s="23"/>
-      <c r="D88" s="23"/>
+      <c r="D88" s="22" t="s">
+        <v>232</v>
+      </c>
     </row>
     <row r="89" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A89" s="23"/>
+      <c r="A89" s="22"/>
       <c r="B89" s="23"/>
       <c r="C89" s="23"/>
       <c r="D89" s="23"/>

--- a/JsonConverter/ExcelFiles/0_MindDialogue.xlsx
+++ b/JsonConverter/ExcelFiles/0_MindDialogue.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\0_SonghaUnityGame\JsonConverter\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2902236-5650-4352-8E20-D1FDAD847967}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF6F4F83-6B7D-4860-AB69-39B43C40924A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="615" yWindow="780" windowWidth="28185" windowHeight="14490" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-240" yWindow="435" windowWidth="28185" windowHeight="14490" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Table_MindDialogue" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="356" uniqueCount="234">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="369" uniqueCount="242">
   <si>
     <t>CharacterDataId</t>
   </si>
@@ -2558,6 +2558,54 @@
   </si>
   <si>
     <t>mindDialogue_Opening_1_1_307</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>mindDialogue_Opening_1_1_307_2</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>좋다! 모두 준비 되었고, 파이팅이다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="3"/>
+      </rPr>
+      <t>!</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>mindDialogue_Opening_1_1_307_3</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>앗! 아직 준비가 안되었다. 까먹은게 있는건가?</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>mindDialogue_Opening_1_1_306</t>
+  </si>
+  <si>
+    <t>mindDialogue_Opening_1_1_307(2)</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>mindDialogue_Opening_1_1_307_2(2)</t>
+  </si>
+  <si>
+    <t>mindDialogue_Opening_1_1_307_2(2)</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -3220,7 +3268,7 @@
   <sheetPr codeName="Sheet1">
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:H1021"/>
+  <dimension ref="A1:H1023"/>
   <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="36.5703125" style="5" customWidth="1"/>
@@ -4688,34 +4736,60 @@
         <v>233</v>
       </c>
       <c r="B88" s="23"/>
-      <c r="C88" s="23"/>
+      <c r="C88" s="22" t="s">
+        <v>239</v>
+      </c>
       <c r="D88" s="22" t="s">
         <v>232</v>
       </c>
     </row>
     <row r="89" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A89" s="22"/>
+      <c r="A89" s="22" t="s">
+        <v>239</v>
+      </c>
       <c r="B89" s="23"/>
       <c r="C89" s="23"/>
-      <c r="D89" s="23"/>
+      <c r="D89" s="22" t="s">
+        <v>232</v>
+      </c>
     </row>
     <row r="90" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A90" s="23"/>
-      <c r="B90" s="23"/>
-      <c r="C90" s="23"/>
-      <c r="D90" s="23"/>
+      <c r="A90" s="22" t="s">
+        <v>234</v>
+      </c>
+      <c r="B90" s="24" t="s">
+        <v>235</v>
+      </c>
+      <c r="C90" s="23" t="s">
+        <v>240</v>
+      </c>
+      <c r="D90" s="22" t="s">
+        <v>232</v>
+      </c>
     </row>
     <row r="91" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A91" s="23"/>
-      <c r="B91" s="23"/>
+      <c r="A91" s="22" t="s">
+        <v>241</v>
+      </c>
+      <c r="B91" s="24"/>
       <c r="C91" s="23"/>
-      <c r="D91" s="23"/>
+      <c r="D91" s="22" t="s">
+        <v>232</v>
+      </c>
     </row>
     <row r="92" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A92" s="23"/>
-      <c r="B92" s="23"/>
-      <c r="C92" s="23"/>
-      <c r="D92" s="23"/>
+      <c r="A92" s="22" t="s">
+        <v>236</v>
+      </c>
+      <c r="B92" s="28" t="s">
+        <v>237</v>
+      </c>
+      <c r="C92" s="23" t="s">
+        <v>238</v>
+      </c>
+      <c r="D92" s="22" t="s">
+        <v>232</v>
+      </c>
     </row>
     <row r="93" spans="1:4" ht="15.75" customHeight="1">
       <c r="A93" s="23"/>
@@ -4787,11 +4861,13 @@
       <c r="A104" s="23"/>
       <c r="B104" s="23"/>
       <c r="C104" s="23"/>
+      <c r="D104" s="23"/>
     </row>
     <row r="105" spans="1:4" ht="15.75" customHeight="1">
       <c r="A105" s="23"/>
       <c r="B105" s="23"/>
       <c r="C105" s="23"/>
+      <c r="D105" s="23"/>
     </row>
     <row r="106" spans="1:4" ht="15.75" customHeight="1">
       <c r="A106" s="23"/>
@@ -4878,8 +4954,16 @@
       <c r="B122" s="23"/>
       <c r="C122" s="23"/>
     </row>
-    <row r="123" spans="1:3" ht="15.75" customHeight="1"/>
-    <row r="124" spans="1:3" ht="15.75" customHeight="1"/>
+    <row r="123" spans="1:3" ht="15.75" customHeight="1">
+      <c r="A123" s="23"/>
+      <c r="B123" s="23"/>
+      <c r="C123" s="23"/>
+    </row>
+    <row r="124" spans="1:3" ht="15.75" customHeight="1">
+      <c r="A124" s="23"/>
+      <c r="B124" s="23"/>
+      <c r="C124" s="23"/>
+    </row>
     <row r="125" spans="1:3" ht="15.75" customHeight="1"/>
     <row r="126" spans="1:3" ht="15.75" customHeight="1"/>
     <row r="127" spans="1:3" ht="15.75" customHeight="1"/>
@@ -5777,6 +5861,8 @@
     <row r="1019" ht="15.75" customHeight="1"/>
     <row r="1020" ht="15.75" customHeight="1"/>
     <row r="1021" ht="15.75" customHeight="1"/>
+    <row r="1022" ht="15.75" customHeight="1"/>
+    <row r="1023" ht="15.75" customHeight="1"/>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.69972223043441772" right="0.69972223043441772" top="0.75" bottom="0.75" header="0.30000001192092896" footer="0.30000001192092896"/>

--- a/JsonConverter/ExcelFiles/0_MindDialogue.xlsx
+++ b/JsonConverter/ExcelFiles/0_MindDialogue.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF6F4F83-6B7D-4860-AB69-39B43C40924A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-240" yWindow="435" windowWidth="28185" windowHeight="14490" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Table_MindDialogue" sheetId="1" r:id="rId1"/>

--- a/JsonConverter/ExcelFiles/0_MindDialogue.xlsx
+++ b/JsonConverter/ExcelFiles/0_MindDialogue.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\0_SonghaUnityGame\JsonConverter\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF6F4F83-6B7D-4860-AB69-39B43C40924A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB808C5C-BC27-4497-8239-EE2254A36E78}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="369" uniqueCount="242">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="387" uniqueCount="254">
   <si>
     <t>CharacterDataId</t>
   </si>
@@ -2607,6 +2607,80 @@
   <si>
     <t>mindDialogue_Opening_1_1_307_2(2)</t>
     <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>mindDialogue_Ending_1_1_13</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">그렇게 내 사랑은 마무리 되었다. </t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>mindDialogue_Ending_1_1_14</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>더 좋은 사람이 되어야 했다…</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>mindDialogue_Ending_1_1_15</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>여전히 나는…</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>부족한 사람이었다.</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Sprite/EndingImage5</t>
+  </si>
+  <si>
+    <t>mindDialogue_Ending_1_2_14</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>그렇게 나는 그녀와 다시 재결합하였고</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>mindDialogue_Ending_1_2_15</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>행복한 나날을 살아가며, 자기 계발을 멈추지  않는 내가 될 것이다.</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Sprite/EndingImage7</t>
   </si>
 </sst>
 </file>
@@ -4792,34 +4866,70 @@
       </c>
     </row>
     <row r="93" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A93" s="23"/>
-      <c r="B93" s="23"/>
-      <c r="C93" s="23"/>
-      <c r="D93" s="23"/>
+      <c r="A93" s="22" t="s">
+        <v>242</v>
+      </c>
+      <c r="B93" s="28" t="s">
+        <v>243</v>
+      </c>
+      <c r="C93" s="22" t="s">
+        <v>244</v>
+      </c>
+      <c r="D93" s="22" t="s">
+        <v>248</v>
+      </c>
     </row>
     <row r="94" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A94" s="23"/>
-      <c r="B94" s="23"/>
-      <c r="C94" s="23"/>
-      <c r="D94" s="23"/>
+      <c r="A94" s="22" t="s">
+        <v>244</v>
+      </c>
+      <c r="B94" s="28" t="s">
+        <v>245</v>
+      </c>
+      <c r="C94" s="22" t="s">
+        <v>246</v>
+      </c>
+      <c r="D94" s="23" t="s">
+        <v>248</v>
+      </c>
     </row>
     <row r="95" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A95" s="23"/>
-      <c r="B95" s="23"/>
+      <c r="A95" s="22" t="s">
+        <v>246</v>
+      </c>
+      <c r="B95" s="24" t="s">
+        <v>247</v>
+      </c>
       <c r="C95" s="23"/>
-      <c r="D95" s="23"/>
+      <c r="D95" s="23" t="s">
+        <v>248</v>
+      </c>
     </row>
     <row r="96" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A96" s="23"/>
-      <c r="B96" s="23"/>
-      <c r="C96" s="23"/>
-      <c r="D96" s="23"/>
+      <c r="A96" s="22" t="s">
+        <v>249</v>
+      </c>
+      <c r="B96" s="28" t="s">
+        <v>250</v>
+      </c>
+      <c r="C96" s="22" t="s">
+        <v>251</v>
+      </c>
+      <c r="D96" s="23" t="s">
+        <v>253</v>
+      </c>
     </row>
     <row r="97" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A97" s="23"/>
-      <c r="B97" s="23"/>
+      <c r="A97" s="22" t="s">
+        <v>251</v>
+      </c>
+      <c r="B97" s="28" t="s">
+        <v>252</v>
+      </c>
       <c r="C97" s="23"/>
-      <c r="D97" s="23"/>
+      <c r="D97" s="23" t="s">
+        <v>253</v>
+      </c>
     </row>
     <row r="98" spans="1:4" ht="15.75" customHeight="1">
       <c r="A98" s="23"/>

--- a/JsonConverter/ExcelFiles/0_MindDialogue.xlsx
+++ b/JsonConverter/ExcelFiles/0_MindDialogue.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\0_SonghaUnityGame\JsonConverter\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB808C5C-BC27-4497-8239-EE2254A36E78}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0E29BAB-053B-4BD5-85A8-C7169A150312}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/JsonConverter/ExcelFiles/0_MindDialogue.xlsx
+++ b/JsonConverter/ExcelFiles/0_MindDialogue.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\0_SonghaUnityGame\JsonConverter\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0E29BAB-053B-4BD5-85A8-C7169A150312}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83681C73-ED81-4839-BE4C-6A22C5946C43}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="390" yWindow="390" windowWidth="28185" windowHeight="14490" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Table_MindDialogue" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="387" uniqueCount="254">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="393" uniqueCount="258">
   <si>
     <t>CharacterDataId</t>
   </si>
@@ -2681,6 +2681,22 @@
   </si>
   <si>
     <t>Sprite/EndingImage7</t>
+  </si>
+  <si>
+    <t>mindDialogue_Ending_1_2_16</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Sprite/EndingImage7</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>mindDialogue_Ending_1_1_16</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Sprite/EndingImage5</t>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -3342,7 +3358,7 @@
   <sheetPr codeName="Sheet1">
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:H1023"/>
+  <dimension ref="A1:H1024"/>
   <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="36.5703125" style="5" customWidth="1"/>
@@ -4900,48 +4916,60 @@
       <c r="B95" s="24" t="s">
         <v>247</v>
       </c>
-      <c r="C95" s="23"/>
-      <c r="D95" s="23" t="s">
-        <v>248</v>
+      <c r="C95" s="22" t="s">
+        <v>256</v>
+      </c>
+      <c r="D95" s="22" t="s">
+        <v>257</v>
       </c>
     </row>
     <row r="96" spans="1:4" ht="15.75" customHeight="1">
       <c r="A96" s="22" t="s">
-        <v>249</v>
-      </c>
-      <c r="B96" s="28" t="s">
-        <v>250</v>
-      </c>
-      <c r="C96" s="22" t="s">
-        <v>251</v>
-      </c>
-      <c r="D96" s="23" t="s">
-        <v>253</v>
+        <v>256</v>
+      </c>
+      <c r="B96" s="24"/>
+      <c r="C96" s="23"/>
+      <c r="D96" s="22" t="s">
+        <v>257</v>
       </c>
     </row>
     <row r="97" spans="1:4" ht="15.75" customHeight="1">
       <c r="A97" s="22" t="s">
+        <v>249</v>
+      </c>
+      <c r="B97" s="28" t="s">
+        <v>250</v>
+      </c>
+      <c r="C97" s="22" t="s">
         <v>251</v>
       </c>
-      <c r="B97" s="28" t="s">
-        <v>252</v>
-      </c>
-      <c r="C97" s="23"/>
       <c r="D97" s="23" t="s">
         <v>253</v>
       </c>
     </row>
     <row r="98" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A98" s="23"/>
-      <c r="B98" s="23"/>
-      <c r="C98" s="23"/>
-      <c r="D98" s="23"/>
+      <c r="A98" s="22" t="s">
+        <v>251</v>
+      </c>
+      <c r="B98" s="28" t="s">
+        <v>252</v>
+      </c>
+      <c r="C98" s="22" t="s">
+        <v>254</v>
+      </c>
+      <c r="D98" s="22" t="s">
+        <v>255</v>
+      </c>
     </row>
     <row r="99" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A99" s="23"/>
+      <c r="A99" s="22" t="s">
+        <v>254</v>
+      </c>
       <c r="B99" s="23"/>
       <c r="C99" s="23"/>
-      <c r="D99" s="23"/>
+      <c r="D99" s="22" t="s">
+        <v>255</v>
+      </c>
     </row>
     <row r="100" spans="1:4" ht="15.75" customHeight="1">
       <c r="A100" s="23"/>
@@ -4983,6 +5011,7 @@
       <c r="A106" s="23"/>
       <c r="B106" s="23"/>
       <c r="C106" s="23"/>
+      <c r="D106" s="23"/>
     </row>
     <row r="107" spans="1:4" ht="15.75" customHeight="1">
       <c r="A107" s="23"/>
@@ -5074,7 +5103,11 @@
       <c r="B124" s="23"/>
       <c r="C124" s="23"/>
     </row>
-    <row r="125" spans="1:3" ht="15.75" customHeight="1"/>
+    <row r="125" spans="1:3" ht="15.75" customHeight="1">
+      <c r="A125" s="23"/>
+      <c r="B125" s="23"/>
+      <c r="C125" s="23"/>
+    </row>
     <row r="126" spans="1:3" ht="15.75" customHeight="1"/>
     <row r="127" spans="1:3" ht="15.75" customHeight="1"/>
     <row r="128" spans="1:3" ht="15.75" customHeight="1"/>
@@ -5973,6 +6006,7 @@
     <row r="1021" ht="15.75" customHeight="1"/>
     <row r="1022" ht="15.75" customHeight="1"/>
     <row r="1023" ht="15.75" customHeight="1"/>
+    <row r="1024" ht="15.75" customHeight="1"/>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.69972223043441772" right="0.69972223043441772" top="0.75" bottom="0.75" header="0.30000001192092896" footer="0.30000001192092896"/>

--- a/JsonConverter/ExcelFiles/0_MindDialogue.xlsx
+++ b/JsonConverter/ExcelFiles/0_MindDialogue.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\0_SonghaUnityGame\JsonConverter\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83681C73-ED81-4839-BE4C-6A22C5946C43}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89D064D6-EA36-49B4-86C5-FF5BA18907F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="390" yWindow="390" windowWidth="28185" windowHeight="14490" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="345" yWindow="870" windowWidth="28185" windowHeight="14490" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Table_MindDialogue" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="393" uniqueCount="258">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="393" uniqueCount="257">
   <si>
     <t>CharacterDataId</t>
   </si>
@@ -2600,9 +2600,6 @@
   <si>
     <t>mindDialogue_Opening_1_1_307(2)</t>
     <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>mindDialogue_Opening_1_1_307_2(2)</t>
   </si>
   <si>
     <t>mindDialogue_Opening_1_1_307_2(2)</t>
@@ -4850,7 +4847,7 @@
       <c r="B90" s="24" t="s">
         <v>235</v>
       </c>
-      <c r="C90" s="23" t="s">
+      <c r="C90" s="22" t="s">
         <v>240</v>
       </c>
       <c r="D90" s="22" t="s">
@@ -4859,7 +4856,7 @@
     </row>
     <row r="91" spans="1:4" ht="15.75" customHeight="1">
       <c r="A91" s="22" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="B91" s="24"/>
       <c r="C91" s="23"/>
@@ -4883,92 +4880,92 @@
     </row>
     <row r="93" spans="1:4" ht="15.75" customHeight="1">
       <c r="A93" s="22" t="s">
+        <v>241</v>
+      </c>
+      <c r="B93" s="28" t="s">
         <v>242</v>
       </c>
-      <c r="B93" s="28" t="s">
+      <c r="C93" s="22" t="s">
         <v>243</v>
       </c>
-      <c r="C93" s="22" t="s">
-        <v>244</v>
-      </c>
       <c r="D93" s="22" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="94" spans="1:4" ht="15.75" customHeight="1">
       <c r="A94" s="22" t="s">
+        <v>243</v>
+      </c>
+      <c r="B94" s="28" t="s">
         <v>244</v>
       </c>
-      <c r="B94" s="28" t="s">
+      <c r="C94" s="22" t="s">
         <v>245</v>
       </c>
-      <c r="C94" s="22" t="s">
-        <v>246</v>
-      </c>
       <c r="D94" s="23" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="95" spans="1:4" ht="15.75" customHeight="1">
       <c r="A95" s="22" t="s">
+        <v>245</v>
+      </c>
+      <c r="B95" s="24" t="s">
         <v>246</v>
       </c>
-      <c r="B95" s="24" t="s">
-        <v>247</v>
-      </c>
       <c r="C95" s="22" t="s">
+        <v>255</v>
+      </c>
+      <c r="D95" s="22" t="s">
         <v>256</v>
-      </c>
-      <c r="D95" s="22" t="s">
-        <v>257</v>
       </c>
     </row>
     <row r="96" spans="1:4" ht="15.75" customHeight="1">
       <c r="A96" s="22" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B96" s="24"/>
       <c r="C96" s="23"/>
       <c r="D96" s="22" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
     </row>
     <row r="97" spans="1:4" ht="15.75" customHeight="1">
       <c r="A97" s="22" t="s">
+        <v>248</v>
+      </c>
+      <c r="B97" s="28" t="s">
         <v>249</v>
       </c>
-      <c r="B97" s="28" t="s">
+      <c r="C97" s="22" t="s">
         <v>250</v>
       </c>
-      <c r="C97" s="22" t="s">
-        <v>251</v>
-      </c>
       <c r="D97" s="23" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
     </row>
     <row r="98" spans="1:4" ht="15.75" customHeight="1">
       <c r="A98" s="22" t="s">
+        <v>250</v>
+      </c>
+      <c r="B98" s="28" t="s">
         <v>251</v>
       </c>
-      <c r="B98" s="28" t="s">
-        <v>252</v>
-      </c>
       <c r="C98" s="22" t="s">
+        <v>253</v>
+      </c>
+      <c r="D98" s="22" t="s">
         <v>254</v>
-      </c>
-      <c r="D98" s="22" t="s">
-        <v>255</v>
       </c>
     </row>
     <row r="99" spans="1:4" ht="15.75" customHeight="1">
       <c r="A99" s="22" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="B99" s="23"/>
       <c r="C99" s="23"/>
       <c r="D99" s="22" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="100" spans="1:4" ht="15.75" customHeight="1">

--- a/JsonConverter/ExcelFiles/0_MindDialogue.xlsx
+++ b/JsonConverter/ExcelFiles/0_MindDialogue.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\0_SonghaUnityGame\JsonConverter\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89D064D6-EA36-49B4-86C5-FF5BA18907F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91526693-7EC7-4389-B647-6DA355B476F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="345" yWindow="870" windowWidth="28185" windowHeight="14490" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="615" yWindow="990" windowWidth="28185" windowHeight="14490" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Table_MindDialogue" sheetId="1" r:id="rId1"/>
@@ -2680,19 +2680,19 @@
     <t>Sprite/EndingImage7</t>
   </si>
   <si>
+    <t>Sprite/EndingImage7</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>mindDialogue_Ending_1_1_16</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Sprite/EndingImage5</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
     <t>mindDialogue_Ending_1_2_16</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Sprite/EndingImage7</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>mindDialogue_Ending_1_1_16</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Sprite/EndingImage5</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -4914,20 +4914,20 @@
         <v>246</v>
       </c>
       <c r="C95" s="22" t="s">
+        <v>254</v>
+      </c>
+      <c r="D95" s="22" t="s">
         <v>255</v>
-      </c>
-      <c r="D95" s="22" t="s">
-        <v>256</v>
       </c>
     </row>
     <row r="96" spans="1:4" ht="15.75" customHeight="1">
       <c r="A96" s="22" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B96" s="24"/>
       <c r="C96" s="23"/>
       <c r="D96" s="22" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
     </row>
     <row r="97" spans="1:4" ht="15.75" customHeight="1">
@@ -4952,24 +4952,24 @@
         <v>251</v>
       </c>
       <c r="C98" s="22" t="s">
+        <v>256</v>
+      </c>
+      <c r="D98" s="22" t="s">
         <v>253</v>
-      </c>
-      <c r="D98" s="22" t="s">
-        <v>254</v>
       </c>
     </row>
     <row r="99" spans="1:4" ht="15.75" customHeight="1">
       <c r="A99" s="22" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="B99" s="23"/>
       <c r="C99" s="23"/>
       <c r="D99" s="22" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
     </row>
     <row r="100" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A100" s="23"/>
+      <c r="A100" s="22"/>
       <c r="B100" s="23"/>
       <c r="C100" s="23"/>
       <c r="D100" s="23"/>
